--- a/Demo/MDA/demo_mda_9999_3_med_treatement.xlsx
+++ b/Demo/MDA/demo_mda_9999_3_med_treatement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D86E49-DFD3-45A0-A2C9-5E9C55F6287C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C726892A-166B-4B50-9C81-4DD72DDB6B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="238">
   <si>
     <t>type</t>
   </si>
@@ -191,12 +191,6 @@
   </si>
   <si>
     <t>no</t>
-  </si>
-  <si>
-    <t>${p_state}</t>
-  </si>
-  <si>
-    <t>${p_location}</t>
   </si>
   <si>
     <t>demo_mda_9999_3_med_treatement</t>
@@ -1360,9 +1354,7 @@
       <c r="P3" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" s="8" t="s">
-        <v>52</v>
-      </c>
+      <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
@@ -1396,9 +1388,7 @@
         <v>38</v>
       </c>
       <c r="Q4" s="8"/>
-      <c r="R4" s="8" t="s">
-        <v>53</v>
-      </c>
+      <c r="R4" s="8"/>
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
@@ -1432,21 +1422,19 @@
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
-      <c r="S5" s="8" t="s">
-        <v>53</v>
-      </c>
+      <c r="S5" s="8"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8"/>
@@ -1471,19 +1459,19 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
       <c r="F7" s="18"/>
       <c r="G7" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -1525,13 +1513,13 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
@@ -1557,10 +1545,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="8"/>
@@ -1588,10 +1576,10 @@
         <v>13</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="8"/>
@@ -1619,10 +1607,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="8"/>
@@ -1650,10 +1638,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="8"/>
@@ -1678,7 +1666,7 @@
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
@@ -1703,20 +1691,20 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
       <c r="H15" s="19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="20"/>
@@ -1737,10 +1725,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="8"/>
@@ -1768,10 +1756,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="8"/>
@@ -1799,10 +1787,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="8"/>
@@ -1830,10 +1818,10 @@
         <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="8"/>
@@ -1858,13 +1846,13 @@
     </row>
     <row r="20" spans="1:21" ht="31.5">
       <c r="A20" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="8"/>
@@ -1872,7 +1860,7 @@
       <c r="G20" s="9"/>
       <c r="H20" s="8"/>
       <c r="I20" s="18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="8"/>
@@ -1889,13 +1877,13 @@
     </row>
     <row r="21" spans="1:21" ht="31.5">
       <c r="A21" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="8"/>
@@ -1903,7 +1891,7 @@
       <c r="G21" s="9"/>
       <c r="H21" s="8"/>
       <c r="I21" s="18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="8"/>
@@ -1923,10 +1911,10 @@
         <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="8"/>
@@ -1954,10 +1942,10 @@
         <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="8"/>
@@ -1985,10 +1973,10 @@
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="8"/>
@@ -2016,10 +2004,10 @@
         <v>13</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
@@ -2047,10 +2035,10 @@
         <v>13</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="8"/>
@@ -2075,7 +2063,7 @@
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="9"/>
@@ -2100,20 +2088,20 @@
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
       <c r="H28" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
@@ -2134,10 +2122,10 @@
         <v>13</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="8"/>
@@ -2165,10 +2153,10 @@
         <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="8"/>
@@ -2196,10 +2184,10 @@
         <v>13</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="8"/>
@@ -2227,10 +2215,10 @@
         <v>13</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="8"/>
@@ -2255,13 +2243,13 @@
     </row>
     <row r="33" spans="1:21" ht="31.5">
       <c r="A33" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="8"/>
@@ -2269,7 +2257,7 @@
       <c r="G33" s="9"/>
       <c r="H33" s="8"/>
       <c r="I33" s="18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="8"/>
@@ -2286,13 +2274,13 @@
     </row>
     <row r="34" spans="1:21" ht="31.5">
       <c r="A34" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="8"/>
@@ -2300,7 +2288,7 @@
       <c r="G34" s="9"/>
       <c r="H34" s="8"/>
       <c r="I34" s="18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J34" s="7"/>
       <c r="K34" s="8"/>
@@ -2320,10 +2308,10 @@
         <v>13</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="8"/>
@@ -2351,10 +2339,10 @@
         <v>13</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="8"/>
@@ -2382,10 +2370,10 @@
         <v>13</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="8"/>
@@ -2413,10 +2401,10 @@
         <v>13</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="8"/>
@@ -2444,10 +2432,10 @@
         <v>13</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="8"/>
@@ -2472,7 +2460,7 @@
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
@@ -2497,20 +2485,20 @@
     </row>
     <row r="41" spans="1:21">
       <c r="A41" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D41" s="19"/>
       <c r="E41" s="19"/>
       <c r="F41" s="19"/>
       <c r="G41" s="19"/>
       <c r="H41" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
@@ -2531,10 +2519,10 @@
         <v>13</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="8"/>
@@ -2562,10 +2550,10 @@
         <v>13</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="8"/>
@@ -2593,10 +2581,10 @@
         <v>13</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="8"/>
@@ -2624,10 +2612,10 @@
         <v>13</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="8"/>
@@ -2652,13 +2640,13 @@
     </row>
     <row r="46" spans="1:21" ht="31.5">
       <c r="A46" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D46" s="9"/>
       <c r="E46" s="8"/>
@@ -2666,7 +2654,7 @@
       <c r="G46" s="9"/>
       <c r="H46" s="8"/>
       <c r="I46" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J46" s="7"/>
       <c r="K46" s="8"/>
@@ -2683,13 +2671,13 @@
     </row>
     <row r="47" spans="1:21" ht="31.5">
       <c r="A47" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="8"/>
@@ -2697,7 +2685,7 @@
       <c r="G47" s="9"/>
       <c r="H47" s="8"/>
       <c r="I47" s="18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J47" s="7"/>
       <c r="K47" s="8"/>
@@ -2717,10 +2705,10 @@
         <v>13</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="8"/>
@@ -2748,10 +2736,10 @@
         <v>13</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="8"/>
@@ -2779,10 +2767,10 @@
         <v>13</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="8"/>
@@ -2810,10 +2798,10 @@
         <v>13</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="8"/>
@@ -2841,10 +2829,10 @@
         <v>13</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D52" s="9"/>
       <c r="E52" s="8"/>
@@ -2869,7 +2857,7 @@
     </row>
     <row r="53" spans="1:21">
       <c r="A53" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
@@ -2894,20 +2882,20 @@
     </row>
     <row r="54" spans="1:21">
       <c r="A54" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D54" s="19"/>
       <c r="E54" s="19"/>
       <c r="F54" s="19"/>
       <c r="G54" s="19"/>
       <c r="H54" s="19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
@@ -2928,10 +2916,10 @@
         <v>13</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="8"/>
@@ -2959,10 +2947,10 @@
         <v>13</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="8"/>
@@ -2990,10 +2978,10 @@
         <v>13</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D57" s="9"/>
       <c r="E57" s="8"/>
@@ -3021,10 +3009,10 @@
         <v>13</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="8"/>
@@ -3049,13 +3037,13 @@
     </row>
     <row r="59" spans="1:21" ht="31.5">
       <c r="A59" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="8"/>
@@ -3063,7 +3051,7 @@
       <c r="G59" s="9"/>
       <c r="H59" s="8"/>
       <c r="I59" s="18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J59" s="7"/>
       <c r="K59" s="8"/>
@@ -3080,13 +3068,13 @@
     </row>
     <row r="60" spans="1:21" ht="31.5">
       <c r="A60" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="8"/>
@@ -3094,7 +3082,7 @@
       <c r="G60" s="9"/>
       <c r="H60" s="8"/>
       <c r="I60" s="18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J60" s="7"/>
       <c r="K60" s="8"/>
@@ -3114,10 +3102,10 @@
         <v>13</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="8"/>
@@ -3145,10 +3133,10 @@
         <v>13</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="8"/>
@@ -3176,10 +3164,10 @@
         <v>13</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D63" s="9"/>
       <c r="E63" s="8"/>
@@ -3207,10 +3195,10 @@
         <v>13</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="8"/>
@@ -3238,10 +3226,10 @@
         <v>13</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D65" s="9"/>
       <c r="E65" s="8"/>
@@ -3266,7 +3254,7 @@
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B66" s="8"/>
       <c r="C66" s="9"/>
@@ -3291,20 +3279,20 @@
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D67" s="19"/>
       <c r="E67" s="19"/>
       <c r="F67" s="19"/>
       <c r="G67" s="19"/>
       <c r="H67" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
@@ -3325,10 +3313,10 @@
         <v>13</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D68" s="9"/>
       <c r="E68" s="8"/>
@@ -3356,10 +3344,10 @@
         <v>13</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="8"/>
@@ -3387,10 +3375,10 @@
         <v>13</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D70" s="9"/>
       <c r="E70" s="8"/>
@@ -3418,10 +3406,10 @@
         <v>13</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D71" s="9"/>
       <c r="E71" s="8"/>
@@ -3446,13 +3434,13 @@
     </row>
     <row r="72" spans="1:21">
       <c r="A72" s="21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D72" s="9"/>
       <c r="E72" s="8"/>
@@ -3460,7 +3448,7 @@
       <c r="G72" s="9"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J72" s="7"/>
       <c r="K72" s="8"/>
@@ -3477,13 +3465,13 @@
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D73" s="9"/>
       <c r="E73" s="8"/>
@@ -3491,7 +3479,7 @@
       <c r="G73" s="9"/>
       <c r="H73" s="8"/>
       <c r="I73" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J73" s="7"/>
       <c r="K73" s="8"/>
@@ -3511,10 +3499,10 @@
         <v>13</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D74" s="9"/>
       <c r="E74" s="8"/>
@@ -3542,10 +3530,10 @@
         <v>13</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="8"/>
@@ -3573,10 +3561,10 @@
         <v>13</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="8"/>
@@ -3604,10 +3592,10 @@
         <v>13</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="8"/>
@@ -3635,10 +3623,10 @@
         <v>13</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="8"/>
@@ -3663,7 +3651,7 @@
     </row>
     <row r="79" spans="1:21">
       <c r="A79" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B79" s="8"/>
       <c r="C79" s="9"/>
@@ -3688,20 +3676,20 @@
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D80" s="19"/>
       <c r="E80" s="19"/>
       <c r="F80" s="19"/>
       <c r="G80" s="19"/>
       <c r="H80" s="19" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
@@ -3722,10 +3710,10 @@
         <v>13</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="8"/>
@@ -3753,10 +3741,10 @@
         <v>13</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="8"/>
@@ -3784,10 +3772,10 @@
         <v>13</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="8"/>
@@ -3815,10 +3803,10 @@
         <v>13</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="8"/>
@@ -3846,10 +3834,10 @@
         <v>13</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="8"/>
@@ -3874,7 +3862,7 @@
     </row>
     <row r="86" spans="1:21">
       <c r="A86" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B86" s="8"/>
       <c r="C86" s="9"/>
@@ -3899,20 +3887,20 @@
     </row>
     <row r="87" spans="1:21">
       <c r="A87" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D87" s="19"/>
       <c r="E87" s="19"/>
       <c r="F87" s="19"/>
       <c r="G87" s="19"/>
       <c r="H87" s="19" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
@@ -3933,10 +3921,10 @@
         <v>13</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="8"/>
@@ -3964,10 +3952,10 @@
         <v>13</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D89" s="9"/>
       <c r="E89" s="8"/>
@@ -3995,10 +3983,10 @@
         <v>13</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D90" s="9"/>
       <c r="E90" s="8"/>
@@ -4026,10 +4014,10 @@
         <v>13</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D91" s="9"/>
       <c r="E91" s="8"/>
@@ -4057,10 +4045,10 @@
         <v>13</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D92" s="9"/>
       <c r="E92" s="8"/>
@@ -4088,10 +4076,10 @@
         <v>13</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D93" s="9"/>
       <c r="E93" s="8"/>
@@ -4119,10 +4107,10 @@
         <v>13</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D94" s="9"/>
       <c r="E94" s="8"/>
@@ -4147,7 +4135,7 @@
     </row>
     <row r="95" spans="1:21">
       <c r="A95" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B95" s="8"/>
       <c r="C95" s="9"/>
@@ -4172,20 +4160,20 @@
     </row>
     <row r="96" spans="1:21">
       <c r="A96" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D96" s="19"/>
       <c r="E96" s="19"/>
       <c r="F96" s="19"/>
       <c r="G96" s="19"/>
       <c r="H96" s="19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
@@ -4206,10 +4194,10 @@
         <v>13</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D97" s="9"/>
       <c r="E97" s="8"/>
@@ -4237,10 +4225,10 @@
         <v>13</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D98" s="9"/>
       <c r="E98" s="8"/>
@@ -4268,10 +4256,10 @@
         <v>13</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D99" s="9"/>
       <c r="E99" s="8"/>
@@ -4299,10 +4287,10 @@
         <v>13</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D100" s="9"/>
       <c r="E100" s="8"/>
@@ -4330,10 +4318,10 @@
         <v>13</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D101" s="9"/>
       <c r="E101" s="8"/>
@@ -4361,10 +4349,10 @@
         <v>13</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D102" s="9"/>
       <c r="E102" s="8"/>
@@ -4392,10 +4380,10 @@
         <v>13</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D103" s="9"/>
       <c r="E103" s="8"/>
@@ -4423,10 +4411,10 @@
         <v>13</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D104" s="9"/>
       <c r="E104" s="8"/>
@@ -4451,7 +4439,7 @@
     </row>
     <row r="105" spans="1:21">
       <c r="A105" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B105" s="8"/>
       <c r="C105" s="9"/>
@@ -4476,20 +4464,20 @@
     </row>
     <row r="106" spans="1:21">
       <c r="A106" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D106" s="19"/>
       <c r="E106" s="19"/>
       <c r="F106" s="19"/>
       <c r="G106" s="19"/>
       <c r="H106" s="19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
@@ -4510,10 +4498,10 @@
         <v>13</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D107" s="9"/>
       <c r="E107" s="8"/>
@@ -4541,10 +4529,10 @@
         <v>13</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D108" s="9"/>
       <c r="E108" s="8"/>
@@ -4572,10 +4560,10 @@
         <v>13</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D109" s="9"/>
       <c r="E109" s="8"/>
@@ -4603,10 +4591,10 @@
         <v>13</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D110" s="9"/>
       <c r="E110" s="8"/>
@@ -4631,7 +4619,7 @@
     </row>
     <row r="111" spans="1:21">
       <c r="A111" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B111" s="8"/>
       <c r="C111" s="9"/>
@@ -4797,112 +4785,112 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="C6" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4912,90 +4900,90 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -5030,10 +5018,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>

--- a/Demo/MDA/demo_mda_9999_3_med_treatement.xlsx
+++ b/Demo/MDA/demo_mda_9999_3_med_treatement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C726892A-166B-4B50-9C81-4DD72DDB6B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2F5B89-AD8A-4881-9DA1-4AE75FE717A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="261">
   <si>
     <t>type</t>
   </si>
@@ -295,9 +295,6 @@
     <t>medicine</t>
   </si>
   <si>
-    <t>Please select the drug(s) you used for the treatment(s)</t>
-  </si>
-  <si>
     <t>dec_by_sex</t>
   </si>
   <si>
@@ -391,51 +388,12 @@
     <t>ALB</t>
   </si>
   <si>
-    <t>ALB (Albendazole alone)</t>
-  </si>
-  <si>
-    <t>DEC</t>
-  </si>
-  <si>
-    <t>DEC (Diethylcarbamazine Citrate alone)</t>
-  </si>
-  <si>
     <t>IVM</t>
   </si>
   <si>
-    <t>IVM (Ivermectin alone)</t>
-  </si>
-  <si>
-    <t>MBD</t>
-  </si>
-  <si>
-    <t>MBD (Mebendazole alone)</t>
-  </si>
-  <si>
     <t>PZQ</t>
   </si>
   <si>
-    <t>PZQ (Praziquantel alone)</t>
-  </si>
-  <si>
-    <t>AZM_tablet</t>
-  </si>
-  <si>
-    <t>AZM (Azithromycin alone) Tablet</t>
-  </si>
-  <si>
-    <t>AZM_suspension</t>
-  </si>
-  <si>
-    <t>AZM (Azithromycin alone) Suspension</t>
-  </si>
-  <si>
-    <t>TETRA</t>
-  </si>
-  <si>
-    <t>TETRA (Tetracycline  alone)</t>
-  </si>
-  <si>
     <t xml:space="preserve">selected(${medicine}, 'MBD') </t>
   </si>
   <si>
@@ -748,7 +706,127 @@
     <t>AZM Report Tablet by sex</t>
   </si>
   <si>
-    <t>You cannot sellect that</t>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>ONCHO</t>
+  </si>
+  <si>
+    <t>SCHISTO</t>
+  </si>
+  <si>
+    <t>STH</t>
+  </si>
+  <si>
+    <t>TRACHOMA</t>
+  </si>
+  <si>
+    <t>IVM+ALB</t>
+  </si>
+  <si>
+    <t>IVM+ALB+DEC</t>
+  </si>
+  <si>
+    <t>TETRA.TAB</t>
+  </si>
+  <si>
+    <t>TETRA TAB</t>
+  </si>
+  <si>
+    <t>TETRA.SUSP</t>
+  </si>
+  <si>
+    <t>TETRA SUSP</t>
+  </si>
+  <si>
+    <t>MEB</t>
+  </si>
+  <si>
+    <t>PZQ+ALB</t>
+  </si>
+  <si>
+    <t>PZQ+MEB</t>
+  </si>
+  <si>
+    <t>select_one recorder_id</t>
+  </si>
+  <si>
+    <t>Select the recorder ID</t>
+  </si>
+  <si>
+    <t>recorder_id</t>
+  </si>
+  <si>
+    <t>p_recorder_id</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>select_multiple disease</t>
+  </si>
+  <si>
+    <t>p_disease</t>
+  </si>
+  <si>
+    <t>Disease covered by the TDM</t>
+  </si>
+  <si>
+    <t>p_medicine</t>
+  </si>
+  <si>
+    <t>Select the meicine package</t>
+  </si>
+  <si>
+    <t>not(selected(${p_medicine}, 'IVM') and not(selected(${p_disease}, 'ONCHO'))) and
+not(selected(${p_medicine}, 'IVM+ALB') and not(selected(${p_disease}, 'LF') or selected(${p_disease}, 'ONCHO'))) and
+not(selected(${p_medicine}, 'IVM+ALB+DEC') and not(selected(${p_disease}, 'LF'))) and
+not(selected(${p_medicine}, 'ALB') and not(selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'MEB') and not(selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'PZQ') and not(selected(${p_disease}, 'SCHISTO'))) and
+not(selected(${p_medicine}, 'PZQ+ALB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'PZQ+MEB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'TETRA.TAB') and not(selected(${p_disease}, 'TRACHOMA'))) and
+not(selected(${p_medicine}, 'TETRA.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))</t>
+  </si>
+  <si>
+    <t>You cannot select a single medicine together with its combination version</t>
   </si>
 </sst>
 </file>
@@ -874,7 +952,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -928,6 +1006,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1206,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U114"/>
+  <dimension ref="A1:U132"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="24.25" style="4" bestFit="1" customWidth="1"/>
@@ -1295,80 +1388,72 @@
       </c>
     </row>
     <row r="2" spans="1:21" s="3" customFormat="1">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+    </row>
+    <row r="3" spans="1:21" s="3" customFormat="1">
+      <c r="A3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="17" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="8"/>
@@ -1385,7 +1470,7 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
@@ -1398,10 +1483,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="8"/>
@@ -1418,7 +1503,7 @@
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
       <c r="P5" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
@@ -1428,13 +1513,13 @@
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="8" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8"/>
@@ -1450,7 +1535,9 @@
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="P6" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
@@ -1459,23 +1546,23 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="8" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="9" t="s">
-        <v>237</v>
-      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="9"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="7"/>
+      <c r="J7" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
@@ -1494,7 +1581,7 @@
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="9"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
@@ -1512,48 +1599,54 @@
       <c r="U8" s="8"/>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-    </row>
-    <row r="10" spans="1:21">
+      <c r="A9" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+    </row>
+    <row r="10" spans="1:21" ht="362.25">
       <c r="A10" s="8" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>212</v>
+        <v>258</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
+      <c r="F10" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>260</v>
+      </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="7" t="s">
@@ -1564,7 +1657,7 @@
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
+      <c r="P10" s="17"/>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
       <c r="S10" s="8"/>
@@ -1572,24 +1665,16 @@
       <c r="U10" s="8"/>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>214</v>
-      </c>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J11" s="7"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -1603,24 +1688,16 @@
       <c r="U11" s="8"/>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>216</v>
-      </c>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
-      <c r="J12" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J12" s="7"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
@@ -1634,24 +1711,16 @@
       <c r="U12" s="8"/>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>54</v>
-      </c>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J13" s="7"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
@@ -1665,14 +1734,12 @@
       <c r="U13" s="8"/>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="8" t="s">
-        <v>83</v>
-      </c>
+      <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
@@ -1690,55 +1757,39 @@
       <c r="U14" s="8"/>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="19"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>78</v>
-      </c>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
-      <c r="J16" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J16" s="7"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
@@ -1752,24 +1803,16 @@
       <c r="U16" s="8"/>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>79</v>
-      </c>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="F17" s="18"/>
       <c r="G17" s="9"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J17" s="7"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
@@ -1783,24 +1826,16 @@
       <c r="U17" s="8"/>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>80</v>
-      </c>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="F18" s="18"/>
       <c r="G18" s="9"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J18" s="7"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
@@ -1814,24 +1849,16 @@
       <c r="U18" s="8"/>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>81</v>
-      </c>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="F19" s="18"/>
       <c r="G19" s="9"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J19" s="7"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
@@ -1844,24 +1871,16 @@
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
     </row>
-    <row r="20" spans="1:21" ht="31.5">
-      <c r="A20" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>71</v>
-      </c>
+    <row r="20" spans="1:21">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="F20" s="18"/>
       <c r="G20" s="9"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="18" t="s">
-        <v>93</v>
-      </c>
+      <c r="I20" s="8"/>
       <c r="J20" s="7"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
@@ -1875,24 +1894,16 @@
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
     </row>
-    <row r="21" spans="1:21" ht="31.5">
-      <c r="A21" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>72</v>
-      </c>
+    <row r="21" spans="1:21">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="F21" s="18"/>
       <c r="G21" s="9"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="18" t="s">
-        <v>95</v>
-      </c>
+      <c r="I21" s="8"/>
       <c r="J21" s="7"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
@@ -1907,24 +1918,16 @@
       <c r="U21" s="8"/>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>73</v>
-      </c>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="F22" s="18"/>
       <c r="G22" s="9"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J22" s="7"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
@@ -1938,24 +1941,16 @@
       <c r="U22" s="8"/>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>74</v>
-      </c>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="F23" s="18"/>
       <c r="G23" s="9"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J23" s="7"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
@@ -1969,24 +1964,16 @@
       <c r="U23" s="8"/>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>75</v>
-      </c>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="9"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J24" s="7"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
@@ -2000,24 +1987,16 @@
       <c r="U24" s="8"/>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>76</v>
-      </c>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="9"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
-      <c r="J25" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J25" s="7"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
@@ -2031,24 +2010,16 @@
       <c r="U25" s="8"/>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>77</v>
-      </c>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J26" s="7"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
@@ -2062,70 +2033,74 @@
       <c r="U26" s="8"/>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
+      <c r="A27" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
+      <c r="A28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="8"/>
@@ -2153,10 +2128,10 @@
         <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="8"/>
@@ -2184,10 +2159,10 @@
         <v>13</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>223</v>
+        <v>69</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="8"/>
@@ -2212,23 +2187,17 @@
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>81</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J32" s="7"/>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
       <c r="M32" s="8"/>
@@ -2241,56 +2210,56 @@
       <c r="T32" s="8"/>
       <c r="U32" s="8"/>
     </row>
-    <row r="33" spans="1:21" ht="31.5">
-      <c r="A33" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="J33" s="7"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="8"/>
-    </row>
-    <row r="34" spans="1:21" ht="31.5">
+    <row r="33" spans="1:21">
+      <c r="A33" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="I33" s="19"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="19"/>
+      <c r="U33" s="19"/>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34" s="8" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>227</v>
+        <v>87</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
       <c r="H34" s="8"/>
-      <c r="I34" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="J34" s="7"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
       <c r="M34" s="8"/>
@@ -2308,10 +2277,10 @@
         <v>13</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>229</v>
+        <v>88</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="8"/>
@@ -2339,10 +2308,10 @@
         <v>13</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>230</v>
+        <v>89</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="8"/>
@@ -2370,10 +2339,10 @@
         <v>13</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>231</v>
+        <v>90</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="8"/>
@@ -2396,25 +2365,25 @@
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" ht="31.5">
       <c r="A38" s="8" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>232</v>
+        <v>91</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
       <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I38" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="J38" s="7"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
       <c r="M38" s="8"/>
@@ -2427,25 +2396,25 @@
       <c r="T38" s="8"/>
       <c r="U38" s="8"/>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" ht="31.5">
       <c r="A39" s="8" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>233</v>
+        <v>93</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
       <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I39" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="J39" s="7"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
       <c r="M39" s="8"/>
@@ -2459,18 +2428,24 @@
       <c r="U39" s="8"/>
     </row>
     <row r="40" spans="1:21">
-      <c r="A40" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9"/>
+      <c r="A40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D40" s="9"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
-      <c r="J40" s="7"/>
+      <c r="J40" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
       <c r="M40" s="8"/>
@@ -2484,45 +2459,45 @@
       <c r="U40" s="8"/>
     </row>
     <row r="41" spans="1:21">
-      <c r="A41" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="I41" s="19"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="19"/>
-      <c r="T41" s="19"/>
-      <c r="U41" s="19"/>
+      <c r="A41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="8"/>
+      <c r="S41" s="8"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="8"/>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="8"/>
@@ -2550,10 +2525,10 @@
         <v>13</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="8"/>
@@ -2581,10 +2556,10 @@
         <v>13</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="8"/>
@@ -2608,24 +2583,18 @@
       <c r="U44" s="8"/>
     </row>
     <row r="45" spans="1:21">
-      <c r="A45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>81</v>
-      </c>
+      <c r="A45" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="8"/>
+      <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J45" s="7"/>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
       <c r="M45" s="8"/>
@@ -2638,56 +2607,56 @@
       <c r="T45" s="8"/>
       <c r="U45" s="8"/>
     </row>
-    <row r="46" spans="1:21" ht="31.5">
-      <c r="A46" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D46" s="9"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="J46" s="7"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
-      <c r="T46" s="8"/>
-      <c r="U46" s="8"/>
-    </row>
-    <row r="47" spans="1:21" ht="31.5">
+    <row r="46" spans="1:21">
+      <c r="A46" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="I46" s="19"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="19"/>
+      <c r="O46" s="19"/>
+      <c r="P46" s="19"/>
+      <c r="Q46" s="19"/>
+      <c r="R46" s="19"/>
+      <c r="S46" s="19"/>
+      <c r="T46" s="19"/>
+      <c r="U46" s="19"/>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47" s="8" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
       <c r="H47" s="8"/>
-      <c r="I47" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="J47" s="7"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
       <c r="M47" s="8"/>
@@ -2705,10 +2674,10 @@
         <v>13</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>112</v>
+        <v>208</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="8"/>
@@ -2736,10 +2705,10 @@
         <v>13</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="8"/>
@@ -2767,10 +2736,10 @@
         <v>13</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>114</v>
+        <v>210</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="8"/>
@@ -2793,25 +2762,25 @@
       <c r="T50" s="8"/>
       <c r="U50" s="8"/>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" ht="31.5">
       <c r="A51" s="8" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>115</v>
+        <v>211</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="9"/>
       <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I51" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="J51" s="7"/>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
       <c r="M51" s="8"/>
@@ -2824,25 +2793,25 @@
       <c r="T51" s="8"/>
       <c r="U51" s="8"/>
     </row>
-    <row r="52" spans="1:21">
+    <row r="52" spans="1:21" ht="31.5">
       <c r="A52" s="8" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D52" s="9"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
       <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I52" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="J52" s="7"/>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
       <c r="M52" s="8"/>
@@ -2856,18 +2825,24 @@
       <c r="U52" s="8"/>
     </row>
     <row r="53" spans="1:21">
-      <c r="A53" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="9"/>
+      <c r="A53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D53" s="9"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="9"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="7"/>
+      <c r="J53" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
       <c r="M53" s="8"/>
@@ -2881,45 +2856,45 @@
       <c r="U53" s="8"/>
     </row>
     <row r="54" spans="1:21">
-      <c r="A54" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="I54" s="19"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="19"/>
-      <c r="L54" s="19"/>
-      <c r="M54" s="19"/>
-      <c r="N54" s="19"/>
-      <c r="O54" s="19"/>
-      <c r="P54" s="19"/>
-      <c r="Q54" s="19"/>
-      <c r="R54" s="19"/>
-      <c r="S54" s="19"/>
-      <c r="T54" s="19"/>
-      <c r="U54" s="19"/>
+      <c r="A54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D54" s="9"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8"/>
+      <c r="Q54" s="8"/>
+      <c r="R54" s="8"/>
+      <c r="S54" s="8"/>
+      <c r="T54" s="8"/>
+      <c r="U54" s="8"/>
     </row>
     <row r="55" spans="1:21">
       <c r="A55" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="8"/>
@@ -2947,10 +2922,10 @@
         <v>13</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="8"/>
@@ -2978,10 +2953,10 @@
         <v>13</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D57" s="9"/>
       <c r="E57" s="8"/>
@@ -3005,24 +2980,18 @@
       <c r="U57" s="8"/>
     </row>
     <row r="58" spans="1:21">
-      <c r="A58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>81</v>
-      </c>
+      <c r="A58" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" s="8"/>
+      <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="9"/>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
-      <c r="J58" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J58" s="7"/>
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
       <c r="M58" s="8"/>
@@ -3035,56 +3004,56 @@
       <c r="T58" s="8"/>
       <c r="U58" s="8"/>
     </row>
-    <row r="59" spans="1:21" ht="31.5">
-      <c r="A59" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D59" s="9"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="J59" s="7"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
-      <c r="M59" s="8"/>
-      <c r="N59" s="8"/>
-      <c r="O59" s="8"/>
-      <c r="P59" s="8"/>
-      <c r="Q59" s="8"/>
-      <c r="R59" s="8"/>
-      <c r="S59" s="8"/>
-      <c r="T59" s="8"/>
-      <c r="U59" s="8"/>
-    </row>
-    <row r="60" spans="1:21" ht="31.5">
+    <row r="59" spans="1:21">
+      <c r="A59" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="I59" s="19"/>
+      <c r="J59" s="20"/>
+      <c r="K59" s="19"/>
+      <c r="L59" s="19"/>
+      <c r="M59" s="19"/>
+      <c r="N59" s="19"/>
+      <c r="O59" s="19"/>
+      <c r="P59" s="19"/>
+      <c r="Q59" s="19"/>
+      <c r="R59" s="19"/>
+      <c r="S59" s="19"/>
+      <c r="T59" s="19"/>
+      <c r="U59" s="19"/>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60" s="8" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
       <c r="G60" s="9"/>
       <c r="H60" s="8"/>
-      <c r="I60" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="J60" s="7"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
       <c r="M60" s="8"/>
@@ -3102,10 +3071,10 @@
         <v>13</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="8"/>
@@ -3133,10 +3102,10 @@
         <v>13</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="8"/>
@@ -3164,10 +3133,10 @@
         <v>13</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D63" s="9"/>
       <c r="E63" s="8"/>
@@ -3190,25 +3159,25 @@
       <c r="T63" s="8"/>
       <c r="U63" s="8"/>
     </row>
-    <row r="64" spans="1:21">
+    <row r="64" spans="1:21" ht="31.5">
       <c r="A64" s="8" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
       <c r="G64" s="9"/>
       <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I64" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="J64" s="7"/>
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
       <c r="M64" s="8"/>
@@ -3221,25 +3190,25 @@
       <c r="T64" s="8"/>
       <c r="U64" s="8"/>
     </row>
-    <row r="65" spans="1:21">
+    <row r="65" spans="1:21" ht="31.5">
       <c r="A65" s="8" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D65" s="9"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="9"/>
       <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I65" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="J65" s="7"/>
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
       <c r="M65" s="8"/>
@@ -3253,18 +3222,24 @@
       <c r="U65" s="8"/>
     </row>
     <row r="66" spans="1:21">
-      <c r="A66" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B66" s="8"/>
-      <c r="C66" s="9"/>
+      <c r="A66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D66" s="9"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
       <c r="G66" s="9"/>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
-      <c r="J66" s="7"/>
+      <c r="J66" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
       <c r="M66" s="8"/>
@@ -3278,45 +3253,45 @@
       <c r="U66" s="8"/>
     </row>
     <row r="67" spans="1:21">
-      <c r="A67" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="I67" s="19"/>
-      <c r="J67" s="20"/>
-      <c r="K67" s="19"/>
-      <c r="L67" s="19"/>
-      <c r="M67" s="19"/>
-      <c r="N67" s="19"/>
-      <c r="O67" s="19"/>
-      <c r="P67" s="19"/>
-      <c r="Q67" s="19"/>
-      <c r="R67" s="19"/>
-      <c r="S67" s="19"/>
-      <c r="T67" s="19"/>
-      <c r="U67" s="19"/>
+      <c r="A67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D67" s="9"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+      <c r="M67" s="8"/>
+      <c r="N67" s="8"/>
+      <c r="O67" s="8"/>
+      <c r="P67" s="8"/>
+      <c r="Q67" s="8"/>
+      <c r="R67" s="8"/>
+      <c r="S67" s="8"/>
+      <c r="T67" s="8"/>
+      <c r="U67" s="8"/>
     </row>
     <row r="68" spans="1:21">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D68" s="9"/>
       <c r="E68" s="8"/>
@@ -3340,14 +3315,14 @@
       <c r="U68" s="8"/>
     </row>
     <row r="69" spans="1:21">
-      <c r="A69" s="21" t="s">
+      <c r="A69" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="8"/>
@@ -3371,14 +3346,14 @@
       <c r="U69" s="8"/>
     </row>
     <row r="70" spans="1:21">
-      <c r="A70" s="21" t="s">
+      <c r="A70" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D70" s="9"/>
       <c r="E70" s="8"/>
@@ -3403,23 +3378,17 @@
     </row>
     <row r="71" spans="1:21">
       <c r="A71" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>81</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B71" s="8"/>
+      <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
       <c r="G71" s="9"/>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
-      <c r="J71" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J71" s="7"/>
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
       <c r="M71" s="8"/>
@@ -3433,55 +3402,55 @@
       <c r="U71" s="8"/>
     </row>
     <row r="72" spans="1:21">
-      <c r="A72" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D72" s="9"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="J72" s="7"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="8"/>
-      <c r="R72" s="8"/>
-      <c r="S72" s="8"/>
-      <c r="T72" s="8"/>
-      <c r="U72" s="8"/>
+      <c r="A72" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="I72" s="19"/>
+      <c r="J72" s="20"/>
+      <c r="K72" s="19"/>
+      <c r="L72" s="19"/>
+      <c r="M72" s="19"/>
+      <c r="N72" s="19"/>
+      <c r="O72" s="19"/>
+      <c r="P72" s="19"/>
+      <c r="Q72" s="19"/>
+      <c r="R72" s="19"/>
+      <c r="S72" s="19"/>
+      <c r="T72" s="19"/>
+      <c r="U72" s="19"/>
     </row>
     <row r="73" spans="1:21">
-      <c r="A73" s="21" t="s">
-        <v>82</v>
+      <c r="A73" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D73" s="9"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="9"/>
       <c r="H73" s="8"/>
-      <c r="I73" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="J73" s="7"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
       <c r="M73" s="8"/>
@@ -3495,14 +3464,14 @@
       <c r="U73" s="8"/>
     </row>
     <row r="74" spans="1:21">
-      <c r="A74" s="21" t="s">
+      <c r="A74" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D74" s="9"/>
       <c r="E74" s="8"/>
@@ -3526,14 +3495,14 @@
       <c r="U74" s="8"/>
     </row>
     <row r="75" spans="1:21">
-      <c r="A75" s="21" t="s">
+      <c r="A75" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="8"/>
@@ -3557,14 +3526,14 @@
       <c r="U75" s="8"/>
     </row>
     <row r="76" spans="1:21">
-      <c r="A76" s="21" t="s">
+      <c r="A76" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="8"/>
@@ -3587,25 +3556,25 @@
       <c r="T76" s="8"/>
       <c r="U76" s="8"/>
     </row>
-    <row r="77" spans="1:21">
-      <c r="A77" s="21" t="s">
-        <v>13</v>
+    <row r="77" spans="1:21" ht="31.5">
+      <c r="A77" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="9"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I77" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="J77" s="7"/>
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
       <c r="M77" s="8"/>
@@ -3618,25 +3587,25 @@
       <c r="T77" s="8"/>
       <c r="U77" s="8"/>
     </row>
-    <row r="78" spans="1:21">
-      <c r="A78" s="21" t="s">
-        <v>13</v>
+    <row r="78" spans="1:21" ht="31.5">
+      <c r="A78" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="9"/>
       <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I78" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="J78" s="7"/>
       <c r="K78" s="8"/>
       <c r="L78" s="8"/>
       <c r="M78" s="8"/>
@@ -3650,18 +3619,24 @@
       <c r="U78" s="8"/>
     </row>
     <row r="79" spans="1:21">
-      <c r="A79" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="9"/>
+      <c r="A79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D79" s="9"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="9"/>
       <c r="H79" s="8"/>
       <c r="I79" s="8"/>
-      <c r="J79" s="7"/>
+      <c r="J79" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
       <c r="M79" s="8"/>
@@ -3675,45 +3650,45 @@
       <c r="U79" s="8"/>
     </row>
     <row r="80" spans="1:21">
-      <c r="A80" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B80" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="I80" s="19"/>
-      <c r="J80" s="20"/>
-      <c r="K80" s="19"/>
-      <c r="L80" s="19"/>
-      <c r="M80" s="19"/>
-      <c r="N80" s="19"/>
-      <c r="O80" s="19"/>
-      <c r="P80" s="19"/>
-      <c r="Q80" s="19"/>
-      <c r="R80" s="19"/>
-      <c r="S80" s="19"/>
-      <c r="T80" s="19"/>
-      <c r="U80" s="19"/>
+      <c r="A80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D80" s="9"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+      <c r="M80" s="8"/>
+      <c r="N80" s="8"/>
+      <c r="O80" s="8"/>
+      <c r="P80" s="8"/>
+      <c r="Q80" s="8"/>
+      <c r="R80" s="8"/>
+      <c r="S80" s="8"/>
+      <c r="T80" s="8"/>
+      <c r="U80" s="8"/>
     </row>
     <row r="81" spans="1:21">
-      <c r="A81" s="21" t="s">
+      <c r="A81" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="8"/>
@@ -3737,14 +3712,14 @@
       <c r="U81" s="8"/>
     </row>
     <row r="82" spans="1:21">
-      <c r="A82" s="21" t="s">
+      <c r="A82" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="8"/>
@@ -3768,14 +3743,14 @@
       <c r="U82" s="8"/>
     </row>
     <row r="83" spans="1:21">
-      <c r="A83" s="21" t="s">
+      <c r="A83" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="8"/>
@@ -3800,23 +3775,17 @@
     </row>
     <row r="84" spans="1:21">
       <c r="A84" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>76</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B84" s="8"/>
+      <c r="C84" s="9"/>
       <c r="D84" s="9"/>
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="9"/>
       <c r="H84" s="8"/>
       <c r="I84" s="8"/>
-      <c r="J84" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J84" s="7"/>
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
       <c r="M84" s="8"/>
@@ -3830,49 +3799,55 @@
       <c r="U84" s="8"/>
     </row>
     <row r="85" spans="1:21">
-      <c r="A85" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D85" s="9"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
-      <c r="N85" s="8"/>
-      <c r="O85" s="8"/>
-      <c r="P85" s="8"/>
-      <c r="Q85" s="8"/>
-      <c r="R85" s="8"/>
-      <c r="S85" s="8"/>
-      <c r="T85" s="8"/>
-      <c r="U85" s="8"/>
+      <c r="A85" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D85" s="19"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I85" s="19"/>
+      <c r="J85" s="20"/>
+      <c r="K85" s="19"/>
+      <c r="L85" s="19"/>
+      <c r="M85" s="19"/>
+      <c r="N85" s="19"/>
+      <c r="O85" s="19"/>
+      <c r="P85" s="19"/>
+      <c r="Q85" s="19"/>
+      <c r="R85" s="19"/>
+      <c r="S85" s="19"/>
+      <c r="T85" s="19"/>
+      <c r="U85" s="19"/>
     </row>
     <row r="86" spans="1:21">
       <c r="A86" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B86" s="8"/>
-      <c r="C86" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="D86" s="9"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
       <c r="G86" s="9"/>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
-      <c r="J86" s="7"/>
+      <c r="J86" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K86" s="8"/>
       <c r="L86" s="8"/>
       <c r="M86" s="8"/>
@@ -3886,45 +3861,45 @@
       <c r="U86" s="8"/>
     </row>
     <row r="87" spans="1:21">
-      <c r="A87" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
-      <c r="H87" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="I87" s="19"/>
-      <c r="J87" s="20"/>
-      <c r="K87" s="19"/>
-      <c r="L87" s="19"/>
-      <c r="M87" s="19"/>
-      <c r="N87" s="19"/>
-      <c r="O87" s="19"/>
-      <c r="P87" s="19"/>
-      <c r="Q87" s="19"/>
-      <c r="R87" s="19"/>
-      <c r="S87" s="19"/>
-      <c r="T87" s="19"/>
-      <c r="U87" s="19"/>
+      <c r="A87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D87" s="9"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="9"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="8"/>
+      <c r="N87" s="8"/>
+      <c r="O87" s="8"/>
+      <c r="P87" s="8"/>
+      <c r="Q87" s="8"/>
+      <c r="R87" s="8"/>
+      <c r="S87" s="8"/>
+      <c r="T87" s="8"/>
+      <c r="U87" s="8"/>
     </row>
     <row r="88" spans="1:21">
       <c r="A88" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="8"/>
@@ -3952,10 +3927,10 @@
         <v>13</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="D89" s="9"/>
       <c r="E89" s="8"/>
@@ -3980,23 +3955,23 @@
     </row>
     <row r="90" spans="1:21">
       <c r="A90" s="21" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D90" s="9"/>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
       <c r="G90" s="9"/>
       <c r="H90" s="8"/>
-      <c r="I90" s="8"/>
-      <c r="J90" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I90" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J90" s="7"/>
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
       <c r="M90" s="8"/>
@@ -4011,23 +3986,23 @@
     </row>
     <row r="91" spans="1:21">
       <c r="A91" s="21" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D91" s="9"/>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
       <c r="G91" s="9"/>
       <c r="H91" s="8"/>
-      <c r="I91" s="8"/>
-      <c r="J91" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I91" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="J91" s="7"/>
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
       <c r="M91" s="8"/>
@@ -4045,10 +4020,10 @@
         <v>13</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D92" s="9"/>
       <c r="E92" s="8"/>
@@ -4076,10 +4051,10 @@
         <v>13</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D93" s="9"/>
       <c r="E93" s="8"/>
@@ -4107,10 +4082,10 @@
         <v>13</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D94" s="9"/>
       <c r="E94" s="8"/>
@@ -4135,17 +4110,23 @@
     </row>
     <row r="95" spans="1:21">
       <c r="A95" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B95" s="8"/>
-      <c r="C95" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="D95" s="9"/>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
       <c r="G95" s="9"/>
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
-      <c r="J95" s="7"/>
+      <c r="J95" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K95" s="8"/>
       <c r="L95" s="8"/>
       <c r="M95" s="8"/>
@@ -4159,55 +4140,49 @@
       <c r="U95" s="8"/>
     </row>
     <row r="96" spans="1:21">
-      <c r="A96" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B96" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C96" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="D96" s="19"/>
-      <c r="E96" s="19"/>
-      <c r="F96" s="19"/>
-      <c r="G96" s="19"/>
-      <c r="H96" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I96" s="19"/>
-      <c r="J96" s="20"/>
-      <c r="K96" s="19"/>
-      <c r="L96" s="19"/>
-      <c r="M96" s="19"/>
-      <c r="N96" s="19"/>
-      <c r="O96" s="19"/>
-      <c r="P96" s="19"/>
-      <c r="Q96" s="19"/>
-      <c r="R96" s="19"/>
-      <c r="S96" s="19"/>
-      <c r="T96" s="19"/>
-      <c r="U96" s="19"/>
+      <c r="A96" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D96" s="9"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="9"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+      <c r="M96" s="8"/>
+      <c r="N96" s="8"/>
+      <c r="O96" s="8"/>
+      <c r="P96" s="8"/>
+      <c r="Q96" s="8"/>
+      <c r="R96" s="8"/>
+      <c r="S96" s="8"/>
+      <c r="T96" s="8"/>
+      <c r="U96" s="8"/>
     </row>
     <row r="97" spans="1:21">
       <c r="A97" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>190</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B97" s="8"/>
+      <c r="C97" s="9"/>
       <c r="D97" s="9"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
       <c r="G97" s="9"/>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
-      <c r="J97" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J97" s="7"/>
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
       <c r="M97" s="8"/>
@@ -4221,45 +4196,45 @@
       <c r="U97" s="8"/>
     </row>
     <row r="98" spans="1:21">
-      <c r="A98" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C98" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D98" s="9"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="8"/>
-      <c r="J98" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
-      <c r="M98" s="8"/>
-      <c r="N98" s="8"/>
-      <c r="O98" s="8"/>
-      <c r="P98" s="8"/>
-      <c r="Q98" s="8"/>
-      <c r="R98" s="8"/>
-      <c r="S98" s="8"/>
-      <c r="T98" s="8"/>
-      <c r="U98" s="8"/>
+      <c r="A98" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="D98" s="19"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="19"/>
+      <c r="G98" s="19"/>
+      <c r="H98" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="I98" s="19"/>
+      <c r="J98" s="20"/>
+      <c r="K98" s="19"/>
+      <c r="L98" s="19"/>
+      <c r="M98" s="19"/>
+      <c r="N98" s="19"/>
+      <c r="O98" s="19"/>
+      <c r="P98" s="19"/>
+      <c r="Q98" s="19"/>
+      <c r="R98" s="19"/>
+      <c r="S98" s="19"/>
+      <c r="T98" s="19"/>
+      <c r="U98" s="19"/>
     </row>
     <row r="99" spans="1:21">
       <c r="A99" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="D99" s="9"/>
       <c r="E99" s="8"/>
@@ -4287,10 +4262,10 @@
         <v>13</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="D100" s="9"/>
       <c r="E100" s="8"/>
@@ -4318,10 +4293,10 @@
         <v>13</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D101" s="9"/>
       <c r="E101" s="8"/>
@@ -4349,10 +4324,10 @@
         <v>13</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D102" s="9"/>
       <c r="E102" s="8"/>
@@ -4380,10 +4355,10 @@
         <v>13</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D103" s="9"/>
       <c r="E103" s="8"/>
@@ -4408,23 +4383,17 @@
     </row>
     <row r="104" spans="1:21">
       <c r="A104" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C104" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B104" s="8"/>
+      <c r="C104" s="9"/>
       <c r="D104" s="9"/>
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
       <c r="G104" s="9"/>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
-      <c r="J104" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J104" s="7"/>
       <c r="K104" s="8"/>
       <c r="L104" s="8"/>
       <c r="M104" s="8"/>
@@ -4438,70 +4407,76 @@
       <c r="U104" s="8"/>
     </row>
     <row r="105" spans="1:21">
-      <c r="A105" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B105" s="8"/>
-      <c r="C105" s="9"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="9"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="8"/>
-      <c r="J105" s="7"/>
-      <c r="K105" s="8"/>
-      <c r="L105" s="8"/>
-      <c r="M105" s="8"/>
-      <c r="N105" s="8"/>
-      <c r="O105" s="8"/>
-      <c r="P105" s="8"/>
-      <c r="Q105" s="8"/>
-      <c r="R105" s="8"/>
-      <c r="S105" s="8"/>
-      <c r="T105" s="8"/>
-      <c r="U105" s="8"/>
+      <c r="A105" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="D105" s="19"/>
+      <c r="E105" s="19"/>
+      <c r="F105" s="19"/>
+      <c r="G105" s="19"/>
+      <c r="H105" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="I105" s="19"/>
+      <c r="J105" s="20"/>
+      <c r="K105" s="19"/>
+      <c r="L105" s="19"/>
+      <c r="M105" s="19"/>
+      <c r="N105" s="19"/>
+      <c r="O105" s="19"/>
+      <c r="P105" s="19"/>
+      <c r="Q105" s="19"/>
+      <c r="R105" s="19"/>
+      <c r="S105" s="19"/>
+      <c r="T105" s="19"/>
+      <c r="U105" s="19"/>
     </row>
     <row r="106" spans="1:21">
-      <c r="A106" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B106" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C106" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="D106" s="19"/>
-      <c r="E106" s="19"/>
-      <c r="F106" s="19"/>
-      <c r="G106" s="19"/>
-      <c r="H106" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I106" s="19"/>
-      <c r="J106" s="20"/>
-      <c r="K106" s="19"/>
-      <c r="L106" s="19"/>
-      <c r="M106" s="19"/>
-      <c r="N106" s="19"/>
-      <c r="O106" s="19"/>
-      <c r="P106" s="19"/>
-      <c r="Q106" s="19"/>
-      <c r="R106" s="19"/>
-      <c r="S106" s="19"/>
-      <c r="T106" s="19"/>
-      <c r="U106" s="19"/>
+      <c r="A106" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D106" s="9"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="9"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="8"/>
+      <c r="J106" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+      <c r="M106" s="8"/>
+      <c r="N106" s="8"/>
+      <c r="O106" s="8"/>
+      <c r="P106" s="8"/>
+      <c r="Q106" s="8"/>
+      <c r="R106" s="8"/>
+      <c r="S106" s="8"/>
+      <c r="T106" s="8"/>
+      <c r="U106" s="8"/>
     </row>
     <row r="107" spans="1:21">
       <c r="A107" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="D107" s="9"/>
       <c r="E107" s="8"/>
@@ -4529,10 +4504,10 @@
         <v>13</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>206</v>
+        <v>73</v>
       </c>
       <c r="D108" s="9"/>
       <c r="E108" s="8"/>
@@ -4560,10 +4535,10 @@
         <v>13</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>208</v>
+        <v>74</v>
       </c>
       <c r="D109" s="9"/>
       <c r="E109" s="8"/>
@@ -4591,10 +4566,10 @@
         <v>13</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="D110" s="9"/>
       <c r="E110" s="8"/>
@@ -4619,17 +4594,23 @@
     </row>
     <row r="111" spans="1:21">
       <c r="A111" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B111" s="8"/>
-      <c r="C111" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="D111" s="9"/>
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
       <c r="G111" s="9"/>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
-      <c r="J111" s="7"/>
+      <c r="J111" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
       <c r="M111" s="8"/>
@@ -4643,14 +4624,14 @@
       <c r="U111" s="8"/>
     </row>
     <row r="112" spans="1:21">
-      <c r="A112" s="8" t="s">
-        <v>16</v>
+      <c r="A112" s="21" t="s">
+        <v>13</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>49</v>
+        <v>169</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D112" s="9"/>
       <c r="E112" s="8"/>
@@ -4659,7 +4640,7 @@
       <c r="H112" s="8"/>
       <c r="I112" s="8"/>
       <c r="J112" s="7" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
@@ -4674,12 +4655,10 @@
       <c r="U112" s="8"/>
     </row>
     <row r="113" spans="1:21">
-      <c r="A113" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B113" s="8" t="s">
-        <v>18</v>
-      </c>
+      <c r="A113" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B113" s="8"/>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
       <c r="E113" s="8"/>
@@ -4687,7 +4666,7 @@
       <c r="G113" s="9"/>
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
-      <c r="J113" s="8"/>
+      <c r="J113" s="7"/>
       <c r="K113" s="8"/>
       <c r="L113" s="8"/>
       <c r="M113" s="8"/>
@@ -4701,31 +4680,573 @@
       <c r="U113" s="8"/>
     </row>
     <row r="114" spans="1:21">
-      <c r="A114" s="8" t="s">
+      <c r="A114" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="D114" s="19"/>
+      <c r="E114" s="19"/>
+      <c r="F114" s="19"/>
+      <c r="G114" s="19"/>
+      <c r="H114" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="I114" s="19"/>
+      <c r="J114" s="20"/>
+      <c r="K114" s="19"/>
+      <c r="L114" s="19"/>
+      <c r="M114" s="19"/>
+      <c r="N114" s="19"/>
+      <c r="O114" s="19"/>
+      <c r="P114" s="19"/>
+      <c r="Q114" s="19"/>
+      <c r="R114" s="19"/>
+      <c r="S114" s="19"/>
+      <c r="T114" s="19"/>
+      <c r="U114" s="19"/>
+    </row>
+    <row r="115" spans="1:21">
+      <c r="A115" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="D115" s="9"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="9"/>
+      <c r="H115" s="8"/>
+      <c r="I115" s="8"/>
+      <c r="J115" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K115" s="8"/>
+      <c r="L115" s="8"/>
+      <c r="M115" s="8"/>
+      <c r="N115" s="8"/>
+      <c r="O115" s="8"/>
+      <c r="P115" s="8"/>
+      <c r="Q115" s="8"/>
+      <c r="R115" s="8"/>
+      <c r="S115" s="8"/>
+      <c r="T115" s="8"/>
+      <c r="U115" s="8"/>
+    </row>
+    <row r="116" spans="1:21">
+      <c r="A116" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D116" s="9"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="8"/>
+      <c r="G116" s="9"/>
+      <c r="H116" s="8"/>
+      <c r="I116" s="8"/>
+      <c r="J116" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K116" s="8"/>
+      <c r="L116" s="8"/>
+      <c r="M116" s="8"/>
+      <c r="N116" s="8"/>
+      <c r="O116" s="8"/>
+      <c r="P116" s="8"/>
+      <c r="Q116" s="8"/>
+      <c r="R116" s="8"/>
+      <c r="S116" s="8"/>
+      <c r="T116" s="8"/>
+      <c r="U116" s="8"/>
+    </row>
+    <row r="117" spans="1:21">
+      <c r="A117" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D117" s="9"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="8"/>
+      <c r="G117" s="9"/>
+      <c r="H117" s="8"/>
+      <c r="I117" s="8"/>
+      <c r="J117" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K117" s="8"/>
+      <c r="L117" s="8"/>
+      <c r="M117" s="8"/>
+      <c r="N117" s="8"/>
+      <c r="O117" s="8"/>
+      <c r="P117" s="8"/>
+      <c r="Q117" s="8"/>
+      <c r="R117" s="8"/>
+      <c r="S117" s="8"/>
+      <c r="T117" s="8"/>
+      <c r="U117" s="8"/>
+    </row>
+    <row r="118" spans="1:21">
+      <c r="A118" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D118" s="9"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="8"/>
+      <c r="G118" s="9"/>
+      <c r="H118" s="8"/>
+      <c r="I118" s="8"/>
+      <c r="J118" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K118" s="8"/>
+      <c r="L118" s="8"/>
+      <c r="M118" s="8"/>
+      <c r="N118" s="8"/>
+      <c r="O118" s="8"/>
+      <c r="P118" s="8"/>
+      <c r="Q118" s="8"/>
+      <c r="R118" s="8"/>
+      <c r="S118" s="8"/>
+      <c r="T118" s="8"/>
+      <c r="U118" s="8"/>
+    </row>
+    <row r="119" spans="1:21">
+      <c r="A119" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D119" s="9"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="8"/>
+      <c r="G119" s="9"/>
+      <c r="H119" s="8"/>
+      <c r="I119" s="8"/>
+      <c r="J119" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K119" s="8"/>
+      <c r="L119" s="8"/>
+      <c r="M119" s="8"/>
+      <c r="N119" s="8"/>
+      <c r="O119" s="8"/>
+      <c r="P119" s="8"/>
+      <c r="Q119" s="8"/>
+      <c r="R119" s="8"/>
+      <c r="S119" s="8"/>
+      <c r="T119" s="8"/>
+      <c r="U119" s="8"/>
+    </row>
+    <row r="120" spans="1:21">
+      <c r="A120" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D120" s="9"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="9"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="8"/>
+      <c r="J120" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K120" s="8"/>
+      <c r="L120" s="8"/>
+      <c r="M120" s="8"/>
+      <c r="N120" s="8"/>
+      <c r="O120" s="8"/>
+      <c r="P120" s="8"/>
+      <c r="Q120" s="8"/>
+      <c r="R120" s="8"/>
+      <c r="S120" s="8"/>
+      <c r="T120" s="8"/>
+      <c r="U120" s="8"/>
+    </row>
+    <row r="121" spans="1:21">
+      <c r="A121" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D121" s="9"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="8"/>
+      <c r="G121" s="9"/>
+      <c r="H121" s="8"/>
+      <c r="I121" s="8"/>
+      <c r="J121" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K121" s="8"/>
+      <c r="L121" s="8"/>
+      <c r="M121" s="8"/>
+      <c r="N121" s="8"/>
+      <c r="O121" s="8"/>
+      <c r="P121" s="8"/>
+      <c r="Q121" s="8"/>
+      <c r="R121" s="8"/>
+      <c r="S121" s="8"/>
+      <c r="T121" s="8"/>
+      <c r="U121" s="8"/>
+    </row>
+    <row r="122" spans="1:21">
+      <c r="A122" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D122" s="9"/>
+      <c r="E122" s="8"/>
+      <c r="F122" s="8"/>
+      <c r="G122" s="9"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="8"/>
+      <c r="J122" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K122" s="8"/>
+      <c r="L122" s="8"/>
+      <c r="M122" s="8"/>
+      <c r="N122" s="8"/>
+      <c r="O122" s="8"/>
+      <c r="P122" s="8"/>
+      <c r="Q122" s="8"/>
+      <c r="R122" s="8"/>
+      <c r="S122" s="8"/>
+      <c r="T122" s="8"/>
+      <c r="U122" s="8"/>
+    </row>
+    <row r="123" spans="1:21">
+      <c r="A123" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B123" s="8"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="8"/>
+      <c r="F123" s="8"/>
+      <c r="G123" s="9"/>
+      <c r="H123" s="8"/>
+      <c r="I123" s="8"/>
+      <c r="J123" s="7"/>
+      <c r="K123" s="8"/>
+      <c r="L123" s="8"/>
+      <c r="M123" s="8"/>
+      <c r="N123" s="8"/>
+      <c r="O123" s="8"/>
+      <c r="P123" s="8"/>
+      <c r="Q123" s="8"/>
+      <c r="R123" s="8"/>
+      <c r="S123" s="8"/>
+      <c r="T123" s="8"/>
+      <c r="U123" s="8"/>
+    </row>
+    <row r="124" spans="1:21">
+      <c r="A124" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="D124" s="19"/>
+      <c r="E124" s="19"/>
+      <c r="F124" s="19"/>
+      <c r="G124" s="19"/>
+      <c r="H124" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="I124" s="19"/>
+      <c r="J124" s="20"/>
+      <c r="K124" s="19"/>
+      <c r="L124" s="19"/>
+      <c r="M124" s="19"/>
+      <c r="N124" s="19"/>
+      <c r="O124" s="19"/>
+      <c r="P124" s="19"/>
+      <c r="Q124" s="19"/>
+      <c r="R124" s="19"/>
+      <c r="S124" s="19"/>
+      <c r="T124" s="19"/>
+      <c r="U124" s="19"/>
+    </row>
+    <row r="125" spans="1:21">
+      <c r="A125" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D125" s="9"/>
+      <c r="E125" s="8"/>
+      <c r="F125" s="8"/>
+      <c r="G125" s="9"/>
+      <c r="H125" s="8"/>
+      <c r="I125" s="8"/>
+      <c r="J125" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K125" s="8"/>
+      <c r="L125" s="8"/>
+      <c r="M125" s="8"/>
+      <c r="N125" s="8"/>
+      <c r="O125" s="8"/>
+      <c r="P125" s="8"/>
+      <c r="Q125" s="8"/>
+      <c r="R125" s="8"/>
+      <c r="S125" s="8"/>
+      <c r="T125" s="8"/>
+      <c r="U125" s="8"/>
+    </row>
+    <row r="126" spans="1:21">
+      <c r="A126" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D126" s="9"/>
+      <c r="E126" s="8"/>
+      <c r="F126" s="8"/>
+      <c r="G126" s="9"/>
+      <c r="H126" s="8"/>
+      <c r="I126" s="8"/>
+      <c r="J126" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K126" s="8"/>
+      <c r="L126" s="8"/>
+      <c r="M126" s="8"/>
+      <c r="N126" s="8"/>
+      <c r="O126" s="8"/>
+      <c r="P126" s="8"/>
+      <c r="Q126" s="8"/>
+      <c r="R126" s="8"/>
+      <c r="S126" s="8"/>
+      <c r="T126" s="8"/>
+      <c r="U126" s="8"/>
+    </row>
+    <row r="127" spans="1:21">
+      <c r="A127" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D127" s="9"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="8"/>
+      <c r="G127" s="9"/>
+      <c r="H127" s="8"/>
+      <c r="I127" s="8"/>
+      <c r="J127" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K127" s="8"/>
+      <c r="L127" s="8"/>
+      <c r="M127" s="8"/>
+      <c r="N127" s="8"/>
+      <c r="O127" s="8"/>
+      <c r="P127" s="8"/>
+      <c r="Q127" s="8"/>
+      <c r="R127" s="8"/>
+      <c r="S127" s="8"/>
+      <c r="T127" s="8"/>
+      <c r="U127" s="8"/>
+    </row>
+    <row r="128" spans="1:21">
+      <c r="A128" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D128" s="9"/>
+      <c r="E128" s="8"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="9"/>
+      <c r="H128" s="8"/>
+      <c r="I128" s="8"/>
+      <c r="J128" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K128" s="8"/>
+      <c r="L128" s="8"/>
+      <c r="M128" s="8"/>
+      <c r="N128" s="8"/>
+      <c r="O128" s="8"/>
+      <c r="P128" s="8"/>
+      <c r="Q128" s="8"/>
+      <c r="R128" s="8"/>
+      <c r="S128" s="8"/>
+      <c r="T128" s="8"/>
+      <c r="U128" s="8"/>
+    </row>
+    <row r="129" spans="1:21">
+      <c r="A129" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B129" s="8"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="8"/>
+      <c r="F129" s="8"/>
+      <c r="G129" s="9"/>
+      <c r="H129" s="8"/>
+      <c r="I129" s="8"/>
+      <c r="J129" s="7"/>
+      <c r="K129" s="8"/>
+      <c r="L129" s="8"/>
+      <c r="M129" s="8"/>
+      <c r="N129" s="8"/>
+      <c r="O129" s="8"/>
+      <c r="P129" s="8"/>
+      <c r="Q129" s="8"/>
+      <c r="R129" s="8"/>
+      <c r="S129" s="8"/>
+      <c r="T129" s="8"/>
+      <c r="U129" s="8"/>
+    </row>
+    <row r="130" spans="1:21">
+      <c r="A130" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D130" s="9"/>
+      <c r="E130" s="8"/>
+      <c r="F130" s="8"/>
+      <c r="G130" s="9"/>
+      <c r="H130" s="8"/>
+      <c r="I130" s="8"/>
+      <c r="J130" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K130" s="8"/>
+      <c r="L130" s="8"/>
+      <c r="M130" s="8"/>
+      <c r="N130" s="8"/>
+      <c r="O130" s="8"/>
+      <c r="P130" s="8"/>
+      <c r="Q130" s="8"/>
+      <c r="R130" s="8"/>
+      <c r="S130" s="8"/>
+      <c r="T130" s="8"/>
+      <c r="U130" s="8"/>
+    </row>
+    <row r="131" spans="1:21">
+      <c r="A131" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="9"/>
+      <c r="H131" s="8"/>
+      <c r="I131" s="8"/>
+      <c r="J131" s="8"/>
+      <c r="K131" s="8"/>
+      <c r="L131" s="8"/>
+      <c r="M131" s="8"/>
+      <c r="N131" s="8"/>
+      <c r="O131" s="8"/>
+      <c r="P131" s="8"/>
+      <c r="Q131" s="8"/>
+      <c r="R131" s="8"/>
+      <c r="S131" s="8"/>
+      <c r="T131" s="8"/>
+      <c r="U131" s="8"/>
+    </row>
+    <row r="132" spans="1:21">
+      <c r="A132" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B114" s="8" t="s">
+      <c r="B132" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
-      <c r="G114" s="9"/>
-      <c r="H114" s="8"/>
-      <c r="I114" s="8"/>
-      <c r="J114" s="8"/>
-      <c r="K114" s="8"/>
-      <c r="L114" s="8"/>
-      <c r="M114" s="8"/>
-      <c r="N114" s="8"/>
-      <c r="O114" s="8"/>
-      <c r="P114" s="8"/>
-      <c r="Q114" s="8"/>
-      <c r="R114" s="8"/>
-      <c r="S114" s="8"/>
-      <c r="T114" s="8"/>
-      <c r="U114" s="8"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
+      <c r="E132" s="8"/>
+      <c r="F132" s="8"/>
+      <c r="G132" s="9"/>
+      <c r="H132" s="8"/>
+      <c r="I132" s="8"/>
+      <c r="J132" s="8"/>
+      <c r="K132" s="8"/>
+      <c r="L132" s="8"/>
+      <c r="M132" s="8"/>
+      <c r="N132" s="8"/>
+      <c r="O132" s="8"/>
+      <c r="P132" s="8"/>
+      <c r="Q132" s="8"/>
+      <c r="R132" s="8"/>
+      <c r="S132" s="8"/>
+      <c r="T132" s="8"/>
+      <c r="U132" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -4736,7 +5257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.625" style="4" bestFit="1" customWidth="1"/>
@@ -4757,238 +5278,468 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B14" s="13">
+        <v>99</v>
+      </c>
+      <c r="C14" s="26">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="26"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="7" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>122</v>
-      </c>
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="8" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="8" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="8" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="9"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="9"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>132</v>
+      <c r="B36" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:C26">
-    <sortCondition ref="B5:B26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:C40">
+    <sortCondition ref="B19:B40"/>
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demo/MDA/demo_mda_9999_3_med_treatement.xlsx
+++ b/Demo/MDA/demo_mda_9999_3_med_treatement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2F5B89-AD8A-4881-9DA1-4AE75FE717A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D8333D-060A-4F6B-92E5-5CCE72CC27C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="267">
   <si>
     <t>type</t>
   </si>
@@ -340,51 +340,6 @@
     <t>DEC By sex</t>
   </si>
   <si>
-    <t xml:space="preserve">selected(${medicine}, 'DEC') </t>
-  </si>
-  <si>
-    <t>mbd_by_sex</t>
-  </si>
-  <si>
-    <t>mbd_5_14_female_treated</t>
-  </si>
-  <si>
-    <t>mbd_5_14_male_treated</t>
-  </si>
-  <si>
-    <t>mbd_15_female_treated</t>
-  </si>
-  <si>
-    <t>mbd_15_male_treated</t>
-  </si>
-  <si>
-    <t>mbd_men_treated</t>
-  </si>
-  <si>
-    <t>${mbd_5_14_male_treated} + ${mbd_15_male_treated}</t>
-  </si>
-  <si>
-    <t>mbd_women_treated</t>
-  </si>
-  <si>
-    <t>${mbd_5_14_female_treated} + ${mbd_15_male_treated}</t>
-  </si>
-  <si>
-    <t>mbd_child</t>
-  </si>
-  <si>
-    <t>mbd_pregnant</t>
-  </si>
-  <si>
-    <t>mbd_breastfeeding</t>
-  </si>
-  <si>
-    <t>mbd_absent</t>
-  </si>
-  <si>
-    <t>mbd_refusal</t>
-  </si>
-  <si>
     <t>ALB</t>
   </si>
   <si>
@@ -394,9 +349,6 @@
     <t>PZQ</t>
   </si>
   <si>
-    <t xml:space="preserve">selected(${medicine}, 'MBD') </t>
-  </si>
-  <si>
     <t>ivm_by_sex</t>
   </si>
   <si>
@@ -442,9 +394,6 @@
     <t>IVM By sex</t>
   </si>
   <si>
-    <t xml:space="preserve">selected(${medicine}, 'IVM') </t>
-  </si>
-  <si>
     <t>pzq_by_sex</t>
   </si>
   <si>
@@ -490,9 +439,6 @@
     <t>PZQ By sex</t>
   </si>
   <si>
-    <t xml:space="preserve">selected(${medicine}, 'PZQ') </t>
-  </si>
-  <si>
     <t>Boys from 6 months to less than 7 years treated</t>
   </si>
   <si>
@@ -508,9 +454,6 @@
     <t>AZM Report Suspension by sex</t>
   </si>
   <si>
-    <t xml:space="preserve">selected(${medicine}, 'AZM_suspension') </t>
-  </si>
-  <si>
     <t>azm_susp_by_sex</t>
   </si>
   <si>
@@ -553,9 +496,6 @@
     <t>Girls more than 7 years treated</t>
   </si>
   <si>
-    <t xml:space="preserve">selected(${medicine}, 'AZM_tablet') </t>
-  </si>
-  <si>
     <t>tetra_by_sex</t>
   </si>
   <si>
@@ -595,9 +535,6 @@
     <t>tetra_refusal</t>
   </si>
   <si>
-    <t xml:space="preserve">selected(${medicine}, 'TETRA') </t>
-  </si>
-  <si>
     <t>cd_who_distributed</t>
   </si>
   <si>
@@ -700,9 +637,6 @@
     <t>ALB By sex</t>
   </si>
   <si>
-    <t xml:space="preserve">selected(${medicine}, 'ALB') </t>
-  </si>
-  <si>
     <t>AZM Report Tablet by sex</t>
   </si>
   <si>
@@ -730,18 +664,6 @@
     <t>IVM+ALB+DEC</t>
   </si>
   <si>
-    <t>TETRA.TAB</t>
-  </si>
-  <si>
-    <t>TETRA TAB</t>
-  </si>
-  <si>
-    <t>TETRA.SUSP</t>
-  </si>
-  <si>
-    <t>TETRA SUSP</t>
-  </si>
-  <si>
     <t>MEB</t>
   </si>
   <si>
@@ -812,6 +734,54 @@
   </si>
   <si>
     <t>Select the meicine package</t>
+  </si>
+  <si>
+    <t>You cannot select a single medicine together with its combination version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${p_medicine}, 'IVM+ALB+DEC') </t>
+  </si>
+  <si>
+    <t>meb_by_sex</t>
+  </si>
+  <si>
+    <t>meb_5_14_female_treated</t>
+  </si>
+  <si>
+    <t>meb_5_14_male_treated</t>
+  </si>
+  <si>
+    <t>meb_15_female_treated</t>
+  </si>
+  <si>
+    <t>meb_15_male_treated</t>
+  </si>
+  <si>
+    <t>meb_men_treated</t>
+  </si>
+  <si>
+    <t>${meb_5_14_male_treated} + ${meb_15_male_treated}</t>
+  </si>
+  <si>
+    <t>meb_women_treated</t>
+  </si>
+  <si>
+    <t>${meb_5_14_female_treated} + ${meb_15_male_treated}</t>
+  </si>
+  <si>
+    <t>meb_child</t>
+  </si>
+  <si>
+    <t>meb_pregnant</t>
+  </si>
+  <si>
+    <t>meb_breastfeeding</t>
+  </si>
+  <si>
+    <t>meb_absent</t>
+  </si>
+  <si>
+    <t>meb_refusal</t>
   </si>
   <si>
     <t>not(selected(${p_medicine}, 'IVM') and not(selected(${p_disease}, 'ONCHO'))) and
@@ -822,11 +792,60 @@
 not(selected(${p_medicine}, 'PZQ') and not(selected(${p_disease}, 'SCHISTO'))) and
 not(selected(${p_medicine}, 'PZQ+ALB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
 not(selected(${p_medicine}, 'PZQ+MEB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
-not(selected(${p_medicine}, 'TETRA.TAB') and not(selected(${p_disease}, 'TRACHOMA'))) and
-not(selected(${p_medicine}, 'TETRA.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))</t>
-  </si>
-  <si>
-    <t>You cannot select a single medicine together with its combination version</t>
+not(selected(${p_medicine}, 'AZM.TAB') and not(selected(${p_disease}, 'TRACHOMA'))) and
+not(selected(${p_medicine}, 'AZM.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))and
+not(selected(${p_medicine}, 'TETRA') and not(selected(${p_disease}, 'TRACHOMA')))</t>
+  </si>
+  <si>
+    <t>TETRA</t>
+  </si>
+  <si>
+    <t>AZM.TAB</t>
+  </si>
+  <si>
+    <t>AZM TAB</t>
+  </si>
+  <si>
+    <t>AZM.SUSP</t>
+  </si>
+  <si>
+    <t>AZM SUSP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${p_medicine}, 'AZM.TAB') </t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${p_medicine}, 'AZM.SUSP') </t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${p_medicine}, 'TETRA') </t>
+  </si>
+  <si>
+    <t>census_method</t>
+  </si>
+  <si>
+    <t>Cencus method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household-Level Digitization </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggregate Reporting </t>
+  </si>
+  <si>
+    <t>select_one census_method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${p_medicine}, 'PZQ+MEB') or selected(${p_medicine}, 'MEB') </t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'IVM') or selected(${p_medicine}, 'IVM+ALB+DEC') or selected(${p_medicine}, 'IVM+ALB')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${p_medicine}, 'IVM+ALB+DEC') or selected(${p_medicine}, 'IVM+ALB') or selected(${p_medicine}, 'ALB') or selected(${p_medicine}, 'PZQ+ALB') </t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${p_medicine}, 'PZQ') or selected(${p_medicine}, 'PZQ+ALB') </t>
   </si>
 </sst>
 </file>
@@ -988,7 +1007,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1299,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U132"/>
+  <dimension ref="A1:U118"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="24.25" style="4" bestFit="1" customWidth="1"/>
@@ -1389,13 +1408,13 @@
     </row>
     <row r="2" spans="1:21" s="3" customFormat="1">
       <c r="A2" s="7" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="7"/>
@@ -1600,13 +1619,13 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="8" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8"/>
@@ -1629,23 +1648,23 @@
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
     </row>
-    <row r="10" spans="1:21" ht="362.25">
+    <row r="10" spans="1:21" ht="393.75">
       <c r="A10" s="8" t="s">
         <v>84</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="8"/>
       <c r="F10" s="18" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -1670,7 +1689,7 @@
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="18"/>
+      <c r="F11" s="8"/>
       <c r="G11" s="9"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -1688,39 +1707,53 @@
       <c r="U11" s="8"/>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
+      <c r="A12" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
+      <c r="A13" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>259</v>
+      </c>
       <c r="D13" s="9"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="18"/>
+      <c r="F13" s="8"/>
       <c r="G13" s="9"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="7"/>
+      <c r="J13" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
@@ -1734,12 +1767,18 @@
       <c r="U13" s="8"/>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>177</v>
+      </c>
       <c r="D14" s="9"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="18"/>
+      <c r="F14" s="8"/>
       <c r="G14" s="9"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
@@ -1757,12 +1796,18 @@
       <c r="U14" s="8"/>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
+      <c r="A15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>179</v>
+      </c>
       <c r="D15" s="9"/>
       <c r="E15" s="8"/>
-      <c r="F15" s="18"/>
+      <c r="F15" s="8"/>
       <c r="G15" s="9"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
@@ -1780,12 +1825,18 @@
       <c r="U15" s="8"/>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
+      <c r="A16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>181</v>
+      </c>
       <c r="D16" s="9"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="18"/>
+      <c r="F16" s="8"/>
       <c r="G16" s="9"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
@@ -1803,12 +1854,18 @@
       <c r="U16" s="8"/>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>54</v>
+      </c>
       <c r="D17" s="9"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="18"/>
+      <c r="F17" s="8"/>
       <c r="G17" s="9"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -1826,12 +1883,14 @@
       <c r="U17" s="8"/>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="8"/>
+      <c r="A18" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="B18" s="8"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="18"/>
+      <c r="F18" s="8"/>
       <c r="G18" s="9"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
@@ -1849,39 +1908,55 @@
       <c r="U18" s="8"/>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
+      <c r="A19" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="D20" s="9"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="18"/>
+      <c r="F20" s="8"/>
       <c r="G20" s="9"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="7"/>
+      <c r="J20" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
@@ -1895,16 +1970,24 @@
       <c r="U20" s="8"/>
     </row>
     <row r="21" spans="1:21">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="D21" s="9"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="18"/>
+      <c r="F21" s="8"/>
       <c r="G21" s="9"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="7"/>
+      <c r="J21" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
@@ -1918,16 +2001,24 @@
       <c r="U21" s="8"/>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="D22" s="9"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="18"/>
+      <c r="F22" s="8"/>
       <c r="G22" s="9"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="7"/>
+      <c r="J22" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
@@ -1941,16 +2032,24 @@
       <c r="U22" s="8"/>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="D23" s="9"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="18"/>
+      <c r="F23" s="8"/>
       <c r="G23" s="9"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="7"/>
+      <c r="J23" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
@@ -1963,16 +2062,24 @@
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
     </row>
-    <row r="24" spans="1:21">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
+    <row r="24" spans="1:21" ht="31.5">
+      <c r="A24" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="D24" s="9"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="18"/>
+      <c r="F24" s="8"/>
       <c r="G24" s="9"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
+      <c r="I24" s="18" t="s">
+        <v>92</v>
+      </c>
       <c r="J24" s="7"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
@@ -1986,16 +2093,24 @@
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
     </row>
-    <row r="25" spans="1:21">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
+    <row r="25" spans="1:21" ht="31.5">
+      <c r="A25" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="18"/>
+      <c r="F25" s="8"/>
       <c r="G25" s="9"/>
       <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
+      <c r="I25" s="18" t="s">
+        <v>94</v>
+      </c>
       <c r="J25" s="7"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
@@ -2010,16 +2125,24 @@
       <c r="U25" s="8"/>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D26" s="9"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="7"/>
+      <c r="J26" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
@@ -2033,43 +2156,45 @@
       <c r="U26" s="8"/>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="19"/>
-      <c r="U27" s="19"/>
+      <c r="A27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="8"/>
@@ -2097,10 +2222,10 @@
         <v>13</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="8"/>
@@ -2128,10 +2253,10 @@
         <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>201</v>
+        <v>99</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="8"/>
@@ -2155,24 +2280,18 @@
       <c r="U30" s="8"/>
     </row>
     <row r="31" spans="1:21">
-      <c r="A31" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>54</v>
-      </c>
+      <c r="A31" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
-      <c r="J31" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J31" s="7"/>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
       <c r="M31" s="8"/>
@@ -2186,70 +2305,76 @@
       <c r="U31" s="8"/>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="8"/>
-      <c r="S32" s="8"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="8"/>
+      <c r="A32" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="I32" s="19"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="I33" s="19"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="T33" s="19"/>
-      <c r="U33" s="19"/>
+      <c r="A33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="8"/>
     </row>
     <row r="34" spans="1:21">
       <c r="A34" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="8"/>
@@ -2277,10 +2402,10 @@
         <v>13</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="8"/>
@@ -2308,10 +2433,10 @@
         <v>13</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="8"/>
@@ -2334,25 +2459,25 @@
       <c r="T36" s="8"/>
       <c r="U36" s="8"/>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" ht="31.5">
       <c r="A37" s="8" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
       <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I37" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="J37" s="7"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
       <c r="M37" s="8"/>
@@ -2370,10 +2495,10 @@
         <v>82</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="8"/>
@@ -2381,7 +2506,7 @@
       <c r="G38" s="9"/>
       <c r="H38" s="8"/>
       <c r="I38" s="18" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="8"/>
@@ -2396,25 +2521,25 @@
       <c r="T38" s="8"/>
       <c r="U38" s="8"/>
     </row>
-    <row r="39" spans="1:21" ht="31.5">
+    <row r="39" spans="1:21">
       <c r="A39" s="8" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>93</v>
+        <v>194</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
       <c r="H39" s="8"/>
-      <c r="I39" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="J39" s="7"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
       <c r="M39" s="8"/>
@@ -2432,10 +2557,10 @@
         <v>13</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="8"/>
@@ -2463,10 +2588,10 @@
         <v>13</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="8"/>
@@ -2494,10 +2619,10 @@
         <v>13</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>97</v>
+        <v>197</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="8"/>
@@ -2525,10 +2650,10 @@
         <v>13</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="8"/>
@@ -2552,24 +2677,18 @@
       <c r="U43" s="8"/>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>77</v>
-      </c>
+      <c r="A44" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
-      <c r="J44" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J44" s="7"/>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
       <c r="M44" s="8"/>
@@ -2583,70 +2702,76 @@
       <c r="U44" s="8"/>
     </row>
     <row r="45" spans="1:21">
-      <c r="A45" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="8"/>
-      <c r="S45" s="8"/>
-      <c r="T45" s="8"/>
-      <c r="U45" s="8"/>
+      <c r="A45" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="I45" s="19"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="19"/>
+      <c r="R45" s="19"/>
+      <c r="S45" s="19"/>
+      <c r="T45" s="19"/>
+      <c r="U45" s="19"/>
     </row>
     <row r="46" spans="1:21">
-      <c r="A46" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="I46" s="19"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="19"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="19"/>
-      <c r="O46" s="19"/>
-      <c r="P46" s="19"/>
-      <c r="Q46" s="19"/>
-      <c r="R46" s="19"/>
-      <c r="S46" s="19"/>
-      <c r="T46" s="19"/>
-      <c r="U46" s="19"/>
+      <c r="A46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" s="9"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="8"/>
+      <c r="S46" s="8"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="8"/>
     </row>
     <row r="47" spans="1:21">
       <c r="A47" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="8"/>
@@ -2674,10 +2799,10 @@
         <v>13</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="8"/>
@@ -2705,10 +2830,10 @@
         <v>13</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="8"/>
@@ -2731,25 +2856,25 @@
       <c r="T49" s="8"/>
       <c r="U49" s="8"/>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" ht="31.5">
       <c r="A50" s="8" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
       <c r="G50" s="9"/>
       <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I50" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="J50" s="7"/>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
       <c r="M50" s="8"/>
@@ -2767,10 +2892,10 @@
         <v>82</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="8"/>
@@ -2778,7 +2903,7 @@
       <c r="G51" s="9"/>
       <c r="H51" s="8"/>
       <c r="I51" s="18" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="J51" s="7"/>
       <c r="K51" s="8"/>
@@ -2793,25 +2918,25 @@
       <c r="T51" s="8"/>
       <c r="U51" s="8"/>
     </row>
-    <row r="52" spans="1:21" ht="31.5">
+    <row r="52" spans="1:21">
       <c r="A52" s="8" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D52" s="9"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
       <c r="H52" s="8"/>
-      <c r="I52" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="J52" s="7"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
       <c r="M52" s="8"/>
@@ -2829,10 +2954,10 @@
         <v>13</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="8"/>
@@ -2860,10 +2985,10 @@
         <v>13</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="8"/>
@@ -2891,10 +3016,10 @@
         <v>13</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="8"/>
@@ -2922,10 +3047,10 @@
         <v>13</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="8"/>
@@ -2949,24 +3074,18 @@
       <c r="U56" s="8"/>
     </row>
     <row r="57" spans="1:21">
-      <c r="A57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>77</v>
-      </c>
+      <c r="A57" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B57" s="8"/>
+      <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="9"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
-      <c r="J57" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J57" s="7"/>
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
       <c r="M57" s="8"/>
@@ -2980,70 +3099,76 @@
       <c r="U57" s="8"/>
     </row>
     <row r="58" spans="1:21">
-      <c r="A58" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="7"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
-      <c r="N58" s="8"/>
-      <c r="O58" s="8"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="8"/>
-      <c r="U58" s="8"/>
+      <c r="A58" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="I58" s="19"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="19"/>
+      <c r="L58" s="19"/>
+      <c r="M58" s="19"/>
+      <c r="N58" s="19"/>
+      <c r="O58" s="19"/>
+      <c r="P58" s="19"/>
+      <c r="Q58" s="19"/>
+      <c r="R58" s="19"/>
+      <c r="S58" s="19"/>
+      <c r="T58" s="19"/>
+      <c r="U58" s="19"/>
     </row>
     <row r="59" spans="1:21">
-      <c r="A59" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="I59" s="19"/>
-      <c r="J59" s="20"/>
-      <c r="K59" s="19"/>
-      <c r="L59" s="19"/>
-      <c r="M59" s="19"/>
-      <c r="N59" s="19"/>
-      <c r="O59" s="19"/>
-      <c r="P59" s="19"/>
-      <c r="Q59" s="19"/>
-      <c r="R59" s="19"/>
-      <c r="S59" s="19"/>
-      <c r="T59" s="19"/>
-      <c r="U59" s="19"/>
+      <c r="A59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59" s="9"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="8"/>
+      <c r="O59" s="8"/>
+      <c r="P59" s="8"/>
+      <c r="Q59" s="8"/>
+      <c r="R59" s="8"/>
+      <c r="S59" s="8"/>
+      <c r="T59" s="8"/>
+      <c r="U59" s="8"/>
     </row>
     <row r="60" spans="1:21">
       <c r="A60" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="8"/>
@@ -3071,10 +3196,10 @@
         <v>13</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="8"/>
@@ -3102,10 +3227,10 @@
         <v>13</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="8"/>
@@ -3128,25 +3253,25 @@
       <c r="T62" s="8"/>
       <c r="U62" s="8"/>
     </row>
-    <row r="63" spans="1:21">
+    <row r="63" spans="1:21" ht="31.5">
       <c r="A63" s="8" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D63" s="9"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
       <c r="G63" s="9"/>
       <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I63" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="J63" s="7"/>
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
       <c r="M63" s="8"/>
@@ -3164,10 +3289,10 @@
         <v>82</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="8"/>
@@ -3175,7 +3300,7 @@
       <c r="G64" s="9"/>
       <c r="H64" s="8"/>
       <c r="I64" s="18" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J64" s="7"/>
       <c r="K64" s="8"/>
@@ -3190,25 +3315,25 @@
       <c r="T64" s="8"/>
       <c r="U64" s="8"/>
     </row>
-    <row r="65" spans="1:21" ht="31.5">
+    <row r="65" spans="1:21">
       <c r="A65" s="8" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D65" s="9"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="9"/>
       <c r="H65" s="8"/>
-      <c r="I65" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J65" s="7"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
       <c r="M65" s="8"/>
@@ -3226,10 +3351,10 @@
         <v>13</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="8"/>
@@ -3257,10 +3382,10 @@
         <v>13</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D67" s="9"/>
       <c r="E67" s="8"/>
@@ -3288,10 +3413,10 @@
         <v>13</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D68" s="9"/>
       <c r="E68" s="8"/>
@@ -3319,10 +3444,10 @@
         <v>13</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="8"/>
@@ -3346,24 +3471,18 @@
       <c r="U69" s="8"/>
     </row>
     <row r="70" spans="1:21">
-      <c r="A70" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>77</v>
-      </c>
+      <c r="A70" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70" s="8"/>
+      <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
       <c r="G70" s="9"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
-      <c r="J70" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J70" s="7"/>
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
       <c r="M70" s="8"/>
@@ -3377,70 +3496,76 @@
       <c r="U70" s="8"/>
     </row>
     <row r="71" spans="1:21">
-      <c r="A71" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
-      <c r="P71" s="8"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="8"/>
-      <c r="U71" s="8"/>
+      <c r="A71" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="I71" s="19"/>
+      <c r="J71" s="20"/>
+      <c r="K71" s="19"/>
+      <c r="L71" s="19"/>
+      <c r="M71" s="19"/>
+      <c r="N71" s="19"/>
+      <c r="O71" s="19"/>
+      <c r="P71" s="19"/>
+      <c r="Q71" s="19"/>
+      <c r="R71" s="19"/>
+      <c r="S71" s="19"/>
+      <c r="T71" s="19"/>
+      <c r="U71" s="19"/>
     </row>
     <row r="72" spans="1:21">
-      <c r="A72" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" s="19" t="s">
+      <c r="A72" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B72" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C72" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="I72" s="19"/>
-      <c r="J72" s="20"/>
-      <c r="K72" s="19"/>
-      <c r="L72" s="19"/>
-      <c r="M72" s="19"/>
-      <c r="N72" s="19"/>
-      <c r="O72" s="19"/>
-      <c r="P72" s="19"/>
-      <c r="Q72" s="19"/>
-      <c r="R72" s="19"/>
-      <c r="S72" s="19"/>
-      <c r="T72" s="19"/>
-      <c r="U72" s="19"/>
+      <c r="C72" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D72" s="9"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
+      <c r="N72" s="8"/>
+      <c r="O72" s="8"/>
+      <c r="P72" s="8"/>
+      <c r="Q72" s="8"/>
+      <c r="R72" s="8"/>
+      <c r="S72" s="8"/>
+      <c r="T72" s="8"/>
+      <c r="U72" s="8"/>
     </row>
     <row r="73" spans="1:21">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>121</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D73" s="9"/>
       <c r="E73" s="8"/>
@@ -3464,14 +3589,14 @@
       <c r="U73" s="8"/>
     </row>
     <row r="74" spans="1:21">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>122</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D74" s="9"/>
       <c r="E74" s="8"/>
@@ -3495,14 +3620,14 @@
       <c r="U74" s="8"/>
     </row>
     <row r="75" spans="1:21">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>123</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="8"/>
@@ -3526,24 +3651,24 @@
       <c r="U75" s="8"/>
     </row>
     <row r="76" spans="1:21">
-      <c r="A76" s="8" t="s">
-        <v>13</v>
+      <c r="A76" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>124</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="9"/>
       <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="I76" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="J76" s="7"/>
       <c r="K76" s="8"/>
       <c r="L76" s="8"/>
       <c r="M76" s="8"/>
@@ -3556,23 +3681,23 @@
       <c r="T76" s="8"/>
       <c r="U76" s="8"/>
     </row>
-    <row r="77" spans="1:21" ht="31.5">
-      <c r="A77" s="8" t="s">
+    <row r="77" spans="1:21">
+      <c r="A77" s="21" t="s">
         <v>82</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="9"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="18" t="s">
-        <v>126</v>
+      <c r="I77" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="J77" s="7"/>
       <c r="K77" s="8"/>
@@ -3587,25 +3712,25 @@
       <c r="T77" s="8"/>
       <c r="U77" s="8"/>
     </row>
-    <row r="78" spans="1:21" ht="31.5">
-      <c r="A78" s="8" t="s">
-        <v>82</v>
+    <row r="78" spans="1:21">
+      <c r="A78" s="21" t="s">
+        <v>13</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="9"/>
       <c r="H78" s="8"/>
-      <c r="I78" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="J78" s="7"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K78" s="8"/>
       <c r="L78" s="8"/>
       <c r="M78" s="8"/>
@@ -3619,14 +3744,14 @@
       <c r="U78" s="8"/>
     </row>
     <row r="79" spans="1:21">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>129</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="8"/>
@@ -3650,14 +3775,14 @@
       <c r="U79" s="8"/>
     </row>
     <row r="80" spans="1:21">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>130</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="8"/>
@@ -3681,14 +3806,14 @@
       <c r="U80" s="8"/>
     </row>
     <row r="81" spans="1:21">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>131</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="8"/>
@@ -3712,14 +3837,14 @@
       <c r="U81" s="8"/>
     </row>
     <row r="82" spans="1:21">
-      <c r="A82" s="8" t="s">
+      <c r="A82" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>132</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="8"/>
@@ -3743,24 +3868,18 @@
       <c r="U82" s="8"/>
     </row>
     <row r="83" spans="1:21">
-      <c r="A83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>77</v>
-      </c>
+      <c r="A83" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="8"/>
+      <c r="C83" s="9"/>
       <c r="D83" s="9"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="9"/>
       <c r="H83" s="8"/>
       <c r="I83" s="8"/>
-      <c r="J83" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J83" s="7"/>
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
       <c r="M83" s="8"/>
@@ -3774,60 +3893,66 @@
       <c r="U83" s="8"/>
     </row>
     <row r="84" spans="1:21">
-      <c r="A84" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="7"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8"/>
-      <c r="N84" s="8"/>
-      <c r="O84" s="8"/>
-      <c r="P84" s="8"/>
-      <c r="Q84" s="8"/>
-      <c r="R84" s="8"/>
-      <c r="S84" s="8"/>
-      <c r="T84" s="8"/>
-      <c r="U84" s="8"/>
+      <c r="A84" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D84" s="19"/>
+      <c r="E84" s="19"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="19"/>
+      <c r="H84" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="I84" s="19"/>
+      <c r="J84" s="20"/>
+      <c r="K84" s="19"/>
+      <c r="L84" s="19"/>
+      <c r="M84" s="19"/>
+      <c r="N84" s="19"/>
+      <c r="O84" s="19"/>
+      <c r="P84" s="19"/>
+      <c r="Q84" s="19"/>
+      <c r="R84" s="19"/>
+      <c r="S84" s="19"/>
+      <c r="T84" s="19"/>
+      <c r="U84" s="19"/>
     </row>
     <row r="85" spans="1:21">
-      <c r="A85" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B85" s="19" t="s">
+      <c r="A85" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B85" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C85" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D85" s="19"/>
-      <c r="E85" s="19"/>
-      <c r="F85" s="19"/>
-      <c r="G85" s="19"/>
-      <c r="H85" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="I85" s="19"/>
-      <c r="J85" s="20"/>
-      <c r="K85" s="19"/>
-      <c r="L85" s="19"/>
-      <c r="M85" s="19"/>
-      <c r="N85" s="19"/>
-      <c r="O85" s="19"/>
-      <c r="P85" s="19"/>
-      <c r="Q85" s="19"/>
-      <c r="R85" s="19"/>
-      <c r="S85" s="19"/>
-      <c r="T85" s="19"/>
-      <c r="U85" s="19"/>
+      <c r="C85" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D85" s="9"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="8"/>
+      <c r="N85" s="8"/>
+      <c r="O85" s="8"/>
+      <c r="P85" s="8"/>
+      <c r="Q85" s="8"/>
+      <c r="R85" s="8"/>
+      <c r="S85" s="8"/>
+      <c r="T85" s="8"/>
+      <c r="U85" s="8"/>
     </row>
     <row r="86" spans="1:21">
       <c r="A86" s="21" t="s">
@@ -3837,7 +3962,7 @@
         <v>137</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="8"/>
@@ -3865,10 +3990,10 @@
         <v>13</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="8"/>
@@ -3896,10 +4021,10 @@
         <v>13</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="8"/>
@@ -3927,10 +4052,10 @@
         <v>13</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D89" s="9"/>
       <c r="E89" s="8"/>
@@ -3955,22 +4080,16 @@
     </row>
     <row r="90" spans="1:21">
       <c r="A90" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>71</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B90" s="8"/>
+      <c r="C90" s="9"/>
       <c r="D90" s="9"/>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
       <c r="G90" s="9"/>
       <c r="H90" s="8"/>
-      <c r="I90" s="8" t="s">
-        <v>142</v>
-      </c>
+      <c r="I90" s="8"/>
       <c r="J90" s="7"/>
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
@@ -3985,45 +4104,45 @@
       <c r="U90" s="8"/>
     </row>
     <row r="91" spans="1:21">
-      <c r="A91" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B91" s="8" t="s">
+      <c r="A91" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="C91" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D91" s="9"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="J91" s="7"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
-      <c r="M91" s="8"/>
-      <c r="N91" s="8"/>
-      <c r="O91" s="8"/>
-      <c r="P91" s="8"/>
-      <c r="Q91" s="8"/>
-      <c r="R91" s="8"/>
-      <c r="S91" s="8"/>
-      <c r="T91" s="8"/>
-      <c r="U91" s="8"/>
+      <c r="C91" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D91" s="19"/>
+      <c r="E91" s="19"/>
+      <c r="F91" s="19"/>
+      <c r="G91" s="19"/>
+      <c r="H91" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="I91" s="19"/>
+      <c r="J91" s="20"/>
+      <c r="K91" s="19"/>
+      <c r="L91" s="19"/>
+      <c r="M91" s="19"/>
+      <c r="N91" s="19"/>
+      <c r="O91" s="19"/>
+      <c r="P91" s="19"/>
+      <c r="Q91" s="19"/>
+      <c r="R91" s="19"/>
+      <c r="S91" s="19"/>
+      <c r="T91" s="19"/>
+      <c r="U91" s="19"/>
     </row>
     <row r="92" spans="1:21">
       <c r="A92" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="D92" s="9"/>
       <c r="E92" s="8"/>
@@ -4051,10 +4170,10 @@
         <v>13</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="D93" s="9"/>
       <c r="E93" s="8"/>
@@ -4082,10 +4201,10 @@
         <v>13</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D94" s="9"/>
       <c r="E94" s="8"/>
@@ -4113,10 +4232,10 @@
         <v>13</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D95" s="9"/>
       <c r="E95" s="8"/>
@@ -4144,10 +4263,10 @@
         <v>13</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D96" s="9"/>
       <c r="E96" s="8"/>
@@ -4172,17 +4291,23 @@
     </row>
     <row r="97" spans="1:21">
       <c r="A97" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B97" s="8"/>
-      <c r="C97" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="D97" s="9"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
       <c r="G97" s="9"/>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
-      <c r="J97" s="7"/>
+      <c r="J97" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
       <c r="M97" s="8"/>
@@ -4196,55 +4321,49 @@
       <c r="U97" s="8"/>
     </row>
     <row r="98" spans="1:21">
-      <c r="A98" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B98" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="19"/>
-      <c r="H98" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="I98" s="19"/>
-      <c r="J98" s="20"/>
-      <c r="K98" s="19"/>
-      <c r="L98" s="19"/>
-      <c r="M98" s="19"/>
-      <c r="N98" s="19"/>
-      <c r="O98" s="19"/>
-      <c r="P98" s="19"/>
-      <c r="Q98" s="19"/>
-      <c r="R98" s="19"/>
-      <c r="S98" s="19"/>
-      <c r="T98" s="19"/>
-      <c r="U98" s="19"/>
+      <c r="A98" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D98" s="9"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+      <c r="M98" s="8"/>
+      <c r="N98" s="8"/>
+      <c r="O98" s="8"/>
+      <c r="P98" s="8"/>
+      <c r="Q98" s="8"/>
+      <c r="R98" s="8"/>
+      <c r="S98" s="8"/>
+      <c r="T98" s="8"/>
+      <c r="U98" s="8"/>
     </row>
     <row r="99" spans="1:21">
       <c r="A99" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="C99" s="9" t="s">
-        <v>152</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B99" s="8"/>
+      <c r="C99" s="9"/>
       <c r="D99" s="9"/>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
       <c r="G99" s="9"/>
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
-      <c r="J99" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J99" s="7"/>
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
       <c r="M99" s="8"/>
@@ -4258,45 +4377,45 @@
       <c r="U99" s="8"/>
     </row>
     <row r="100" spans="1:21">
-      <c r="A100" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C100" s="9" t="s">
+      <c r="A100" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B100" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="D100" s="9"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8"/>
-      <c r="J100" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="8"/>
-      <c r="N100" s="8"/>
-      <c r="O100" s="8"/>
-      <c r="P100" s="8"/>
-      <c r="Q100" s="8"/>
-      <c r="R100" s="8"/>
-      <c r="S100" s="8"/>
-      <c r="T100" s="8"/>
-      <c r="U100" s="8"/>
+      <c r="C100" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="D100" s="19"/>
+      <c r="E100" s="19"/>
+      <c r="F100" s="19"/>
+      <c r="G100" s="19"/>
+      <c r="H100" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="I100" s="19"/>
+      <c r="J100" s="20"/>
+      <c r="K100" s="19"/>
+      <c r="L100" s="19"/>
+      <c r="M100" s="19"/>
+      <c r="N100" s="19"/>
+      <c r="O100" s="19"/>
+      <c r="P100" s="19"/>
+      <c r="Q100" s="19"/>
+      <c r="R100" s="19"/>
+      <c r="S100" s="19"/>
+      <c r="T100" s="19"/>
+      <c r="U100" s="19"/>
     </row>
     <row r="101" spans="1:21">
       <c r="A101" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="D101" s="9"/>
       <c r="E101" s="8"/>
@@ -4324,10 +4443,10 @@
         <v>13</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="D102" s="9"/>
       <c r="E102" s="8"/>
@@ -4355,10 +4474,10 @@
         <v>13</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="D103" s="9"/>
       <c r="E103" s="8"/>
@@ -4383,17 +4502,23 @@
     </row>
     <row r="104" spans="1:21">
       <c r="A104" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B104" s="8"/>
-      <c r="C104" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D104" s="9"/>
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
       <c r="G104" s="9"/>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
-      <c r="J104" s="7"/>
+      <c r="J104" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K104" s="8"/>
       <c r="L104" s="8"/>
       <c r="M104" s="8"/>
@@ -4407,35 +4532,35 @@
       <c r="U104" s="8"/>
     </row>
     <row r="105" spans="1:21">
-      <c r="A105" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B105" s="19" t="s">
+      <c r="A105" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B105" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C105" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="D105" s="19"/>
-      <c r="E105" s="19"/>
-      <c r="F105" s="19"/>
-      <c r="G105" s="19"/>
-      <c r="H105" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="I105" s="19"/>
-      <c r="J105" s="20"/>
-      <c r="K105" s="19"/>
-      <c r="L105" s="19"/>
-      <c r="M105" s="19"/>
-      <c r="N105" s="19"/>
-      <c r="O105" s="19"/>
-      <c r="P105" s="19"/>
-      <c r="Q105" s="19"/>
-      <c r="R105" s="19"/>
-      <c r="S105" s="19"/>
-      <c r="T105" s="19"/>
-      <c r="U105" s="19"/>
+      <c r="C105" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D105" s="9"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="9"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+      <c r="M105" s="8"/>
+      <c r="N105" s="8"/>
+      <c r="O105" s="8"/>
+      <c r="P105" s="8"/>
+      <c r="Q105" s="8"/>
+      <c r="R105" s="8"/>
+      <c r="S105" s="8"/>
+      <c r="T105" s="8"/>
+      <c r="U105" s="8"/>
     </row>
     <row r="106" spans="1:21">
       <c r="A106" s="21" t="s">
@@ -4445,7 +4570,7 @@
         <v>163</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="D106" s="9"/>
       <c r="E106" s="8"/>
@@ -4476,7 +4601,7 @@
         <v>164</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="D107" s="9"/>
       <c r="E107" s="8"/>
@@ -4507,7 +4632,7 @@
         <v>165</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D108" s="9"/>
       <c r="E108" s="8"/>
@@ -4532,23 +4657,17 @@
     </row>
     <row r="109" spans="1:21">
       <c r="A109" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B109" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C109" s="9" t="s">
-        <v>74</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B109" s="8"/>
+      <c r="C109" s="9"/>
       <c r="D109" s="9"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
       <c r="G109" s="9"/>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
-      <c r="J109" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J109" s="7"/>
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
       <c r="M109" s="8"/>
@@ -4562,35 +4681,33 @@
       <c r="U109" s="8"/>
     </row>
     <row r="110" spans="1:21">
-      <c r="A110" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B110" s="8" t="s">
+      <c r="A110" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C110" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="C110" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D110" s="9"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8"/>
-      <c r="J110" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
-      <c r="M110" s="8"/>
-      <c r="N110" s="8"/>
-      <c r="O110" s="8"/>
-      <c r="P110" s="8"/>
-      <c r="Q110" s="8"/>
-      <c r="R110" s="8"/>
-      <c r="S110" s="8"/>
-      <c r="T110" s="8"/>
-      <c r="U110" s="8"/>
+      <c r="D110" s="19"/>
+      <c r="E110" s="19"/>
+      <c r="F110" s="19"/>
+      <c r="G110" s="19"/>
+      <c r="H110" s="19"/>
+      <c r="I110" s="19"/>
+      <c r="J110" s="20"/>
+      <c r="K110" s="19"/>
+      <c r="L110" s="19"/>
+      <c r="M110" s="19"/>
+      <c r="N110" s="19"/>
+      <c r="O110" s="19"/>
+      <c r="P110" s="19"/>
+      <c r="Q110" s="19"/>
+      <c r="R110" s="19"/>
+      <c r="S110" s="19"/>
+      <c r="T110" s="19"/>
+      <c r="U110" s="19"/>
     </row>
     <row r="111" spans="1:21">
       <c r="A111" s="21" t="s">
@@ -4600,7 +4717,7 @@
         <v>168</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="D111" s="9"/>
       <c r="E111" s="8"/>
@@ -4628,10 +4745,10 @@
         <v>13</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="D112" s="9"/>
       <c r="E112" s="8"/>
@@ -4656,17 +4773,23 @@
     </row>
     <row r="113" spans="1:21">
       <c r="A113" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B113" s="8"/>
-      <c r="C113" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>173</v>
+      </c>
       <c r="D113" s="9"/>
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
       <c r="G113" s="9"/>
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
-      <c r="J113" s="7"/>
+      <c r="J113" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K113" s="8"/>
       <c r="L113" s="8"/>
       <c r="M113" s="8"/>
@@ -4680,55 +4803,49 @@
       <c r="U113" s="8"/>
     </row>
     <row r="114" spans="1:21">
-      <c r="A114" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B114" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C114" s="19" t="s">
+      <c r="A114" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B114" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D114" s="19"/>
-      <c r="E114" s="19"/>
-      <c r="F114" s="19"/>
-      <c r="G114" s="19"/>
-      <c r="H114" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="I114" s="19"/>
-      <c r="J114" s="20"/>
-      <c r="K114" s="19"/>
-      <c r="L114" s="19"/>
-      <c r="M114" s="19"/>
-      <c r="N114" s="19"/>
-      <c r="O114" s="19"/>
-      <c r="P114" s="19"/>
-      <c r="Q114" s="19"/>
-      <c r="R114" s="19"/>
-      <c r="S114" s="19"/>
-      <c r="T114" s="19"/>
-      <c r="U114" s="19"/>
+      <c r="C114" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D114" s="9"/>
+      <c r="E114" s="8"/>
+      <c r="F114" s="8"/>
+      <c r="G114" s="9"/>
+      <c r="H114" s="8"/>
+      <c r="I114" s="8"/>
+      <c r="J114" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K114" s="8"/>
+      <c r="L114" s="8"/>
+      <c r="M114" s="8"/>
+      <c r="N114" s="8"/>
+      <c r="O114" s="8"/>
+      <c r="P114" s="8"/>
+      <c r="Q114" s="8"/>
+      <c r="R114" s="8"/>
+      <c r="S114" s="8"/>
+      <c r="T114" s="8"/>
+      <c r="U114" s="8"/>
     </row>
     <row r="115" spans="1:21">
       <c r="A115" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B115" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C115" s="9" t="s">
-        <v>176</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B115" s="8"/>
+      <c r="C115" s="9"/>
       <c r="D115" s="9"/>
       <c r="E115" s="8"/>
       <c r="F115" s="8"/>
       <c r="G115" s="9"/>
       <c r="H115" s="8"/>
       <c r="I115" s="8"/>
-      <c r="J115" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J115" s="7"/>
       <c r="K115" s="8"/>
       <c r="L115" s="8"/>
       <c r="M115" s="8"/>
@@ -4742,14 +4859,14 @@
       <c r="U115" s="8"/>
     </row>
     <row r="116" spans="1:21">
-      <c r="A116" s="21" t="s">
-        <v>13</v>
+      <c r="A116" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>177</v>
+        <v>49</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D116" s="9"/>
       <c r="E116" s="8"/>
@@ -4758,7 +4875,7 @@
       <c r="H116" s="8"/>
       <c r="I116" s="8"/>
       <c r="J116" s="7" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="K116" s="8"/>
       <c r="L116" s="8"/>
@@ -4773,24 +4890,20 @@
       <c r="U116" s="8"/>
     </row>
     <row r="117" spans="1:21">
-      <c r="A117" s="21" t="s">
-        <v>13</v>
+      <c r="A117" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>180</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
       <c r="G117" s="9"/>
       <c r="H117" s="8"/>
       <c r="I117" s="8"/>
-      <c r="J117" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J117" s="8"/>
       <c r="K117" s="8"/>
       <c r="L117" s="8"/>
       <c r="M117" s="8"/>
@@ -4804,24 +4917,20 @@
       <c r="U117" s="8"/>
     </row>
     <row r="118" spans="1:21">
-      <c r="A118" s="21" t="s">
-        <v>13</v>
+      <c r="A118" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C118" s="9" t="s">
-        <v>73</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C118" s="9"/>
       <c r="D118" s="9"/>
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
       <c r="G118" s="9"/>
       <c r="H118" s="8"/>
       <c r="I118" s="8"/>
-      <c r="J118" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J118" s="8"/>
       <c r="K118" s="8"/>
       <c r="L118" s="8"/>
       <c r="M118" s="8"/>
@@ -4834,420 +4943,6 @@
       <c r="T118" s="8"/>
       <c r="U118" s="8"/>
     </row>
-    <row r="119" spans="1:21">
-      <c r="A119" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B119" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C119" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D119" s="9"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
-      <c r="G119" s="9"/>
-      <c r="H119" s="8"/>
-      <c r="I119" s="8"/>
-      <c r="J119" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K119" s="8"/>
-      <c r="L119" s="8"/>
-      <c r="M119" s="8"/>
-      <c r="N119" s="8"/>
-      <c r="O119" s="8"/>
-      <c r="P119" s="8"/>
-      <c r="Q119" s="8"/>
-      <c r="R119" s="8"/>
-      <c r="S119" s="8"/>
-      <c r="T119" s="8"/>
-      <c r="U119" s="8"/>
-    </row>
-    <row r="120" spans="1:21">
-      <c r="A120" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B120" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C120" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D120" s="9"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="8"/>
-      <c r="G120" s="9"/>
-      <c r="H120" s="8"/>
-      <c r="I120" s="8"/>
-      <c r="J120" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K120" s="8"/>
-      <c r="L120" s="8"/>
-      <c r="M120" s="8"/>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
-      <c r="P120" s="8"/>
-      <c r="Q120" s="8"/>
-      <c r="R120" s="8"/>
-      <c r="S120" s="8"/>
-      <c r="T120" s="8"/>
-      <c r="U120" s="8"/>
-    </row>
-    <row r="121" spans="1:21">
-      <c r="A121" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C121" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D121" s="9"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
-      <c r="G121" s="9"/>
-      <c r="H121" s="8"/>
-      <c r="I121" s="8"/>
-      <c r="J121" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K121" s="8"/>
-      <c r="L121" s="8"/>
-      <c r="M121" s="8"/>
-      <c r="N121" s="8"/>
-      <c r="O121" s="8"/>
-      <c r="P121" s="8"/>
-      <c r="Q121" s="8"/>
-      <c r="R121" s="8"/>
-      <c r="S121" s="8"/>
-      <c r="T121" s="8"/>
-      <c r="U121" s="8"/>
-    </row>
-    <row r="122" spans="1:21">
-      <c r="A122" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B122" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C122" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D122" s="9"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
-      <c r="G122" s="9"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="8"/>
-      <c r="J122" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K122" s="8"/>
-      <c r="L122" s="8"/>
-      <c r="M122" s="8"/>
-      <c r="N122" s="8"/>
-      <c r="O122" s="8"/>
-      <c r="P122" s="8"/>
-      <c r="Q122" s="8"/>
-      <c r="R122" s="8"/>
-      <c r="S122" s="8"/>
-      <c r="T122" s="8"/>
-      <c r="U122" s="8"/>
-    </row>
-    <row r="123" spans="1:21">
-      <c r="A123" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B123" s="8"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="8"/>
-      <c r="J123" s="7"/>
-      <c r="K123" s="8"/>
-      <c r="L123" s="8"/>
-      <c r="M123" s="8"/>
-      <c r="N123" s="8"/>
-      <c r="O123" s="8"/>
-      <c r="P123" s="8"/>
-      <c r="Q123" s="8"/>
-      <c r="R123" s="8"/>
-      <c r="S123" s="8"/>
-      <c r="T123" s="8"/>
-      <c r="U123" s="8"/>
-    </row>
-    <row r="124" spans="1:21">
-      <c r="A124" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B124" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C124" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="D124" s="19"/>
-      <c r="E124" s="19"/>
-      <c r="F124" s="19"/>
-      <c r="G124" s="19"/>
-      <c r="H124" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="I124" s="19"/>
-      <c r="J124" s="20"/>
-      <c r="K124" s="19"/>
-      <c r="L124" s="19"/>
-      <c r="M124" s="19"/>
-      <c r="N124" s="19"/>
-      <c r="O124" s="19"/>
-      <c r="P124" s="19"/>
-      <c r="Q124" s="19"/>
-      <c r="R124" s="19"/>
-      <c r="S124" s="19"/>
-      <c r="T124" s="19"/>
-      <c r="U124" s="19"/>
-    </row>
-    <row r="125" spans="1:21">
-      <c r="A125" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B125" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="C125" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D125" s="9"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
-      <c r="G125" s="9"/>
-      <c r="H125" s="8"/>
-      <c r="I125" s="8"/>
-      <c r="J125" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K125" s="8"/>
-      <c r="L125" s="8"/>
-      <c r="M125" s="8"/>
-      <c r="N125" s="8"/>
-      <c r="O125" s="8"/>
-      <c r="P125" s="8"/>
-      <c r="Q125" s="8"/>
-      <c r="R125" s="8"/>
-      <c r="S125" s="8"/>
-      <c r="T125" s="8"/>
-      <c r="U125" s="8"/>
-    </row>
-    <row r="126" spans="1:21">
-      <c r="A126" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B126" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C126" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D126" s="9"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
-      <c r="G126" s="9"/>
-      <c r="H126" s="8"/>
-      <c r="I126" s="8"/>
-      <c r="J126" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K126" s="8"/>
-      <c r="L126" s="8"/>
-      <c r="M126" s="8"/>
-      <c r="N126" s="8"/>
-      <c r="O126" s="8"/>
-      <c r="P126" s="8"/>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="8"/>
-      <c r="S126" s="8"/>
-      <c r="T126" s="8"/>
-      <c r="U126" s="8"/>
-    </row>
-    <row r="127" spans="1:21">
-      <c r="A127" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B127" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="C127" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D127" s="9"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
-      <c r="G127" s="9"/>
-      <c r="H127" s="8"/>
-      <c r="I127" s="8"/>
-      <c r="J127" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K127" s="8"/>
-      <c r="L127" s="8"/>
-      <c r="M127" s="8"/>
-      <c r="N127" s="8"/>
-      <c r="O127" s="8"/>
-      <c r="P127" s="8"/>
-      <c r="Q127" s="8"/>
-      <c r="R127" s="8"/>
-      <c r="S127" s="8"/>
-      <c r="T127" s="8"/>
-      <c r="U127" s="8"/>
-    </row>
-    <row r="128" spans="1:21">
-      <c r="A128" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B128" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C128" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="D128" s="9"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
-      <c r="G128" s="9"/>
-      <c r="H128" s="8"/>
-      <c r="I128" s="8"/>
-      <c r="J128" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K128" s="8"/>
-      <c r="L128" s="8"/>
-      <c r="M128" s="8"/>
-      <c r="N128" s="8"/>
-      <c r="O128" s="8"/>
-      <c r="P128" s="8"/>
-      <c r="Q128" s="8"/>
-      <c r="R128" s="8"/>
-      <c r="S128" s="8"/>
-      <c r="T128" s="8"/>
-      <c r="U128" s="8"/>
-    </row>
-    <row r="129" spans="1:21">
-      <c r="A129" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B129" s="8"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
-      <c r="G129" s="9"/>
-      <c r="H129" s="8"/>
-      <c r="I129" s="8"/>
-      <c r="J129" s="7"/>
-      <c r="K129" s="8"/>
-      <c r="L129" s="8"/>
-      <c r="M129" s="8"/>
-      <c r="N129" s="8"/>
-      <c r="O129" s="8"/>
-      <c r="P129" s="8"/>
-      <c r="Q129" s="8"/>
-      <c r="R129" s="8"/>
-      <c r="S129" s="8"/>
-      <c r="T129" s="8"/>
-      <c r="U129" s="8"/>
-    </row>
-    <row r="130" spans="1:21">
-      <c r="A130" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B130" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C130" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D130" s="9"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
-      <c r="G130" s="9"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="8"/>
-      <c r="J130" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K130" s="8"/>
-      <c r="L130" s="8"/>
-      <c r="M130" s="8"/>
-      <c r="N130" s="8"/>
-      <c r="O130" s="8"/>
-      <c r="P130" s="8"/>
-      <c r="Q130" s="8"/>
-      <c r="R130" s="8"/>
-      <c r="S130" s="8"/>
-      <c r="T130" s="8"/>
-      <c r="U130" s="8"/>
-    </row>
-    <row r="131" spans="1:21">
-      <c r="A131" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B131" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C131" s="9"/>
-      <c r="D131" s="9"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
-      <c r="G131" s="9"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="8"/>
-      <c r="J131" s="8"/>
-      <c r="K131" s="8"/>
-      <c r="L131" s="8"/>
-      <c r="M131" s="8"/>
-      <c r="N131" s="8"/>
-      <c r="O131" s="8"/>
-      <c r="P131" s="8"/>
-      <c r="Q131" s="8"/>
-      <c r="R131" s="8"/>
-      <c r="S131" s="8"/>
-      <c r="T131" s="8"/>
-      <c r="U131" s="8"/>
-    </row>
-    <row r="132" spans="1:21">
-      <c r="A132" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B132" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
-      <c r="G132" s="9"/>
-      <c r="H132" s="8"/>
-      <c r="I132" s="8"/>
-      <c r="J132" s="8"/>
-      <c r="K132" s="8"/>
-      <c r="L132" s="8"/>
-      <c r="M132" s="8"/>
-      <c r="N132" s="8"/>
-      <c r="O132" s="8"/>
-      <c r="P132" s="8"/>
-      <c r="Q132" s="8"/>
-      <c r="R132" s="8"/>
-      <c r="S132" s="8"/>
-      <c r="T132" s="8"/>
-      <c r="U132" s="8"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5257,11 +4952,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21" style="4" customWidth="1"/>
+    <col min="2" max="2" width="29.125" style="4" customWidth="1"/>
     <col min="3" max="3" width="33.75" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="11" style="4"/>
   </cols>
@@ -5279,139 +4974,139 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="13" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B14" s="13">
         <v>99</v>
@@ -5569,57 +5264,57 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="8" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="8" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="8" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="8" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="8" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5632,10 +5327,10 @@
         <v>85</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -5643,10 +5338,10 @@
         <v>85</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -5654,10 +5349,10 @@
         <v>85</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -5665,10 +5360,10 @@
         <v>85</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -5676,10 +5371,10 @@
         <v>85</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -5687,10 +5382,10 @@
         <v>85</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -5698,10 +5393,10 @@
         <v>85</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -5709,10 +5404,10 @@
         <v>85</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>118</v>
+        <v>209</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>118</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -5720,10 +5415,10 @@
         <v>85</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>236</v>
+        <v>103</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>236</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -5731,10 +5426,48 @@
         <v>85</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>237</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="9"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -5743,6 +5476,7 @@
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Demo/MDA/demo_mda_9999_3_med_treatement.xlsx
+++ b/Demo/MDA/demo_mda_9999_3_med_treatement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D8333D-060A-4F6B-92E5-5CCE72CC27C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5C9231-EDA2-49E9-8F3F-03A8B9709DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -193,12 +193,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>demo_mda_9999_3_med_treatement</t>
-  </si>
-  <si>
-    <t>(Demo) 3. MDA Medicine Treatement Form</t>
-  </si>
-  <si>
     <t>Population under 5 years old</t>
   </si>
   <si>
@@ -846,6 +840,12 @@
   </si>
   <si>
     <t xml:space="preserve">selected(${p_medicine}, 'PZQ') or selected(${p_medicine}, 'PZQ+ALB') </t>
+  </si>
+  <si>
+    <t>(Demo) 3. MDA Medicine Treatement Form V2</t>
+  </si>
+  <si>
+    <t>demo_mda_9999_3_med_treatement_v2</t>
   </si>
 </sst>
 </file>
@@ -1408,13 +1408,13 @@
     </row>
     <row r="2" spans="1:21" s="3" customFormat="1">
       <c r="A2" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="7"/>
@@ -1565,13 +1565,13 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
@@ -1619,13 +1619,13 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8"/>
@@ -1650,21 +1650,21 @@
     </row>
     <row r="10" spans="1:21" ht="393.75">
       <c r="A10" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="8"/>
       <c r="F10" s="18" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -1708,13 +1708,13 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
@@ -1737,13 +1737,13 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="8"/>
@@ -1771,10 +1771,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="8"/>
@@ -1800,10 +1800,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="8"/>
@@ -1829,10 +1829,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="8"/>
@@ -1858,10 +1858,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="8"/>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="9"/>
@@ -1909,20 +1909,20 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19"/>
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
       <c r="H19" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
@@ -1943,10 +1943,10 @@
         <v>13</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="8"/>
@@ -1974,10 +1974,10 @@
         <v>13</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="8"/>
@@ -2005,10 +2005,10 @@
         <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="8"/>
@@ -2036,10 +2036,10 @@
         <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="8"/>
@@ -2064,13 +2064,13 @@
     </row>
     <row r="24" spans="1:21" ht="31.5">
       <c r="A24" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="8"/>
@@ -2078,7 +2078,7 @@
       <c r="G24" s="9"/>
       <c r="H24" s="8"/>
       <c r="I24" s="18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="8"/>
@@ -2095,13 +2095,13 @@
     </row>
     <row r="25" spans="1:21" ht="31.5">
       <c r="A25" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
@@ -2109,7 +2109,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="8"/>
       <c r="I25" s="18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="8"/>
@@ -2129,10 +2129,10 @@
         <v>13</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="8"/>
@@ -2160,10 +2160,10 @@
         <v>13</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="8"/>
@@ -2191,10 +2191,10 @@
         <v>13</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="8"/>
@@ -2222,10 +2222,10 @@
         <v>13</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="8"/>
@@ -2253,10 +2253,10 @@
         <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="8"/>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="9"/>
@@ -2306,20 +2306,20 @@
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
@@ -2340,10 +2340,10 @@
         <v>13</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="8"/>
@@ -2371,10 +2371,10 @@
         <v>13</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="8"/>
@@ -2402,10 +2402,10 @@
         <v>13</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="8"/>
@@ -2433,10 +2433,10 @@
         <v>13</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="8"/>
@@ -2461,13 +2461,13 @@
     </row>
     <row r="37" spans="1:21" ht="31.5">
       <c r="A37" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="8"/>
@@ -2475,7 +2475,7 @@
       <c r="G37" s="9"/>
       <c r="H37" s="8"/>
       <c r="I37" s="18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J37" s="7"/>
       <c r="K37" s="8"/>
@@ -2492,13 +2492,13 @@
     </row>
     <row r="38" spans="1:21" ht="31.5">
       <c r="A38" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="8"/>
@@ -2506,7 +2506,7 @@
       <c r="G38" s="9"/>
       <c r="H38" s="8"/>
       <c r="I38" s="18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="8"/>
@@ -2526,10 +2526,10 @@
         <v>13</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="8"/>
@@ -2557,10 +2557,10 @@
         <v>13</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="8"/>
@@ -2588,10 +2588,10 @@
         <v>13</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="8"/>
@@ -2619,10 +2619,10 @@
         <v>13</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="8"/>
@@ -2650,10 +2650,10 @@
         <v>13</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="8"/>
@@ -2678,7 +2678,7 @@
     </row>
     <row r="44" spans="1:21">
       <c r="A44" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
@@ -2703,20 +2703,20 @@
     </row>
     <row r="45" spans="1:21">
       <c r="A45" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D45" s="19"/>
       <c r="E45" s="19"/>
       <c r="F45" s="19"/>
       <c r="G45" s="19"/>
       <c r="H45" s="19" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
@@ -2737,10 +2737,10 @@
         <v>13</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D46" s="9"/>
       <c r="E46" s="8"/>
@@ -2768,10 +2768,10 @@
         <v>13</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="8"/>
@@ -2799,10 +2799,10 @@
         <v>13</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="8"/>
@@ -2830,10 +2830,10 @@
         <v>13</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="8"/>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="50" spans="1:21" ht="31.5">
       <c r="A50" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="8"/>
@@ -2872,7 +2872,7 @@
       <c r="G50" s="9"/>
       <c r="H50" s="8"/>
       <c r="I50" s="18" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J50" s="7"/>
       <c r="K50" s="8"/>
@@ -2889,13 +2889,13 @@
     </row>
     <row r="51" spans="1:21" ht="31.5">
       <c r="A51" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="8"/>
@@ -2903,7 +2903,7 @@
       <c r="G51" s="9"/>
       <c r="H51" s="8"/>
       <c r="I51" s="18" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J51" s="7"/>
       <c r="K51" s="8"/>
@@ -2923,10 +2923,10 @@
         <v>13</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D52" s="9"/>
       <c r="E52" s="8"/>
@@ -2954,10 +2954,10 @@
         <v>13</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="8"/>
@@ -2985,10 +2985,10 @@
         <v>13</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="8"/>
@@ -3016,10 +3016,10 @@
         <v>13</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="8"/>
@@ -3047,10 +3047,10 @@
         <v>13</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="8"/>
@@ -3075,7 +3075,7 @@
     </row>
     <row r="57" spans="1:21">
       <c r="A57" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
@@ -3100,20 +3100,20 @@
     </row>
     <row r="58" spans="1:21">
       <c r="A58" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D58" s="19"/>
       <c r="E58" s="19"/>
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
       <c r="H58" s="19" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
@@ -3134,10 +3134,10 @@
         <v>13</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="8"/>
@@ -3165,10 +3165,10 @@
         <v>13</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="8"/>
@@ -3196,10 +3196,10 @@
         <v>13</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="8"/>
@@ -3227,10 +3227,10 @@
         <v>13</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="8"/>
@@ -3255,13 +3255,13 @@
     </row>
     <row r="63" spans="1:21" ht="31.5">
       <c r="A63" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D63" s="9"/>
       <c r="E63" s="8"/>
@@ -3269,7 +3269,7 @@
       <c r="G63" s="9"/>
       <c r="H63" s="8"/>
       <c r="I63" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J63" s="7"/>
       <c r="K63" s="8"/>
@@ -3286,13 +3286,13 @@
     </row>
     <row r="64" spans="1:21" ht="31.5">
       <c r="A64" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="8"/>
@@ -3300,7 +3300,7 @@
       <c r="G64" s="9"/>
       <c r="H64" s="8"/>
       <c r="I64" s="18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J64" s="7"/>
       <c r="K64" s="8"/>
@@ -3320,10 +3320,10 @@
         <v>13</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D65" s="9"/>
       <c r="E65" s="8"/>
@@ -3351,10 +3351,10 @@
         <v>13</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="8"/>
@@ -3382,10 +3382,10 @@
         <v>13</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D67" s="9"/>
       <c r="E67" s="8"/>
@@ -3413,10 +3413,10 @@
         <v>13</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D68" s="9"/>
       <c r="E68" s="8"/>
@@ -3444,10 +3444,10 @@
         <v>13</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="8"/>
@@ -3472,7 +3472,7 @@
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="9"/>
@@ -3497,20 +3497,20 @@
     </row>
     <row r="71" spans="1:21">
       <c r="A71" s="22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D71" s="19"/>
       <c r="E71" s="19"/>
       <c r="F71" s="19"/>
       <c r="G71" s="19"/>
       <c r="H71" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
@@ -3531,10 +3531,10 @@
         <v>13</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D72" s="9"/>
       <c r="E72" s="8"/>
@@ -3562,10 +3562,10 @@
         <v>13</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D73" s="9"/>
       <c r="E73" s="8"/>
@@ -3593,10 +3593,10 @@
         <v>13</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D74" s="9"/>
       <c r="E74" s="8"/>
@@ -3624,10 +3624,10 @@
         <v>13</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="8"/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="76" spans="1:21">
       <c r="A76" s="21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="8"/>
@@ -3666,7 +3666,7 @@
       <c r="G76" s="9"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J76" s="7"/>
       <c r="K76" s="8"/>
@@ -3683,13 +3683,13 @@
     </row>
     <row r="77" spans="1:21">
       <c r="A77" s="21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="8"/>
@@ -3697,7 +3697,7 @@
       <c r="G77" s="9"/>
       <c r="H77" s="8"/>
       <c r="I77" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J77" s="7"/>
       <c r="K77" s="8"/>
@@ -3717,10 +3717,10 @@
         <v>13</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="8"/>
@@ -3748,10 +3748,10 @@
         <v>13</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="8"/>
@@ -3779,10 +3779,10 @@
         <v>13</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="8"/>
@@ -3810,10 +3810,10 @@
         <v>13</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="8"/>
@@ -3841,10 +3841,10 @@
         <v>13</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="8"/>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="83" spans="1:21">
       <c r="A83" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B83" s="8"/>
       <c r="C83" s="9"/>
@@ -3894,20 +3894,20 @@
     </row>
     <row r="84" spans="1:21">
       <c r="A84" s="22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D84" s="19"/>
       <c r="E84" s="19"/>
       <c r="F84" s="19"/>
       <c r="G84" s="19"/>
       <c r="H84" s="19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
@@ -3928,10 +3928,10 @@
         <v>13</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="8"/>
@@ -3959,10 +3959,10 @@
         <v>13</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="8"/>
@@ -3990,10 +3990,10 @@
         <v>13</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="8"/>
@@ -4021,10 +4021,10 @@
         <v>13</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="8"/>
@@ -4052,10 +4052,10 @@
         <v>13</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D89" s="9"/>
       <c r="E89" s="8"/>
@@ -4080,7 +4080,7 @@
     </row>
     <row r="90" spans="1:21">
       <c r="A90" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B90" s="8"/>
       <c r="C90" s="9"/>
@@ -4105,20 +4105,20 @@
     </row>
     <row r="91" spans="1:21">
       <c r="A91" s="22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D91" s="19"/>
       <c r="E91" s="19"/>
       <c r="F91" s="19"/>
       <c r="G91" s="19"/>
       <c r="H91" s="19" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
@@ -4139,10 +4139,10 @@
         <v>13</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D92" s="9"/>
       <c r="E92" s="8"/>
@@ -4170,10 +4170,10 @@
         <v>13</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D93" s="9"/>
       <c r="E93" s="8"/>
@@ -4201,10 +4201,10 @@
         <v>13</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D94" s="9"/>
       <c r="E94" s="8"/>
@@ -4232,10 +4232,10 @@
         <v>13</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D95" s="9"/>
       <c r="E95" s="8"/>
@@ -4263,10 +4263,10 @@
         <v>13</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D96" s="9"/>
       <c r="E96" s="8"/>
@@ -4294,10 +4294,10 @@
         <v>13</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D97" s="9"/>
       <c r="E97" s="8"/>
@@ -4325,10 +4325,10 @@
         <v>13</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D98" s="9"/>
       <c r="E98" s="8"/>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="99" spans="1:21">
       <c r="A99" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B99" s="8"/>
       <c r="C99" s="9"/>
@@ -4378,20 +4378,20 @@
     </row>
     <row r="100" spans="1:21">
       <c r="A100" s="22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D100" s="19"/>
       <c r="E100" s="19"/>
       <c r="F100" s="19"/>
       <c r="G100" s="19"/>
       <c r="H100" s="19" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
@@ -4412,10 +4412,10 @@
         <v>13</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D101" s="9"/>
       <c r="E101" s="8"/>
@@ -4443,10 +4443,10 @@
         <v>13</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D102" s="9"/>
       <c r="E102" s="8"/>
@@ -4474,10 +4474,10 @@
         <v>13</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D103" s="9"/>
       <c r="E103" s="8"/>
@@ -4505,10 +4505,10 @@
         <v>13</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D104" s="9"/>
       <c r="E104" s="8"/>
@@ -4536,10 +4536,10 @@
         <v>13</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D105" s="9"/>
       <c r="E105" s="8"/>
@@ -4567,10 +4567,10 @@
         <v>13</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D106" s="9"/>
       <c r="E106" s="8"/>
@@ -4598,10 +4598,10 @@
         <v>13</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D107" s="9"/>
       <c r="E107" s="8"/>
@@ -4629,10 +4629,10 @@
         <v>13</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D108" s="9"/>
       <c r="E108" s="8"/>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="109" spans="1:21">
       <c r="A109" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B109" s="8"/>
       <c r="C109" s="9"/>
@@ -4682,13 +4682,13 @@
     </row>
     <row r="110" spans="1:21">
       <c r="A110" s="22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D110" s="19"/>
       <c r="E110" s="19"/>
@@ -4714,10 +4714,10 @@
         <v>13</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D111" s="9"/>
       <c r="E111" s="8"/>
@@ -4745,10 +4745,10 @@
         <v>13</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D112" s="9"/>
       <c r="E112" s="8"/>
@@ -4776,10 +4776,10 @@
         <v>13</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D113" s="9"/>
       <c r="E113" s="8"/>
@@ -4807,10 +4807,10 @@
         <v>13</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D114" s="9"/>
       <c r="E114" s="8"/>
@@ -4835,7 +4835,7 @@
     </row>
     <row r="115" spans="1:21">
       <c r="A115" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B115" s="8"/>
       <c r="C115" s="9"/>
@@ -4974,139 +4974,139 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="B2" s="24" t="s">
-        <v>216</v>
-      </c>
       <c r="C2" s="25" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B14" s="13">
         <v>99</v>
@@ -5149,112 +5149,112 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="C20" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5264,57 +5264,57 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>203</v>
-      </c>
       <c r="C31" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -5324,123 +5324,123 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -5450,24 +5450,24 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>260</v>
-      </c>
       <c r="C48" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -5486,7 +5486,7 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="53.375" customWidth="1"/>
-    <col min="2" max="2" width="33.375" customWidth="1"/>
+    <col min="2" max="2" width="37.75" customWidth="1"/>
     <col min="3" max="3" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5503,10 +5503,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>265</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>266</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
